--- a/MERN_Stack_4_Month_Attendance_Sheet (2).xlsx
+++ b/MERN_Stack_4_Month_Attendance_Sheet (2).xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="51">
   <si>
     <t>MERN STACK COURSE — MONTH 4 ATTENDANCE</t>
   </si>
@@ -179,6 +179,9 @@
   </si>
   <si>
     <t>_</t>
+  </si>
+  <si>
+    <t>Introduction to HTTP and HTTPS Uses and Applications</t>
   </si>
   <si>
     <t>How to use: Enter the course start date in the yellow cell, add the topic for each class, and select P, A, or L from the Attendance dropdown. The summary updates automatically.</t>
@@ -1211,10 +1214,18 @@
         <f>IF(A16="","",TEXT(A16,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="49"/>
+      <c r="C16" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="48">
+        <v>46023.791666666664</v>
+      </c>
+      <c r="F16" s="49">
+        <v>46023.833333333336</v>
+      </c>
       <c r="G16" s="10">
         <f>IF(D16="P",1,0)</f>
       </c>
@@ -4105,7 +4116,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75" customFormat="1" s="40">
       <c r="A133" s="51" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B133" s="52"/>
       <c r="C133" s="46"/>

--- a/MERN_Stack_4_Month_Attendance_Sheet (2).xlsx
+++ b/MERN_Stack_4_Month_Attendance_Sheet (2).xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="52">
   <si>
     <t>MERN STACK COURSE — MONTH 4 ATTENDANCE</t>
   </si>
@@ -148,7 +148,7 @@
     <t>Batch / Mode</t>
   </si>
   <si>
-    <t>Online / Offline</t>
+    <t>Online</t>
   </si>
   <si>
     <t>Course Start Date</t>
@@ -175,13 +175,16 @@
     <t>-</t>
   </si>
   <si>
-    <t>l</t>
-  </si>
-  <si>
     <t>_</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>Introduction to HTTP and HTTPS Uses and Applications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTML tags </t>
   </si>
   <si>
     <t>How to use: Enter the course start date in the yellow cell, add the topic for each class, and select P, A, or L from the Attendance dropdown. The summary updates automatically.</t>
@@ -198,7 +201,7 @@
     <numFmt numFmtId="167" formatCode="h:mm Am/Pm"/>
     <numFmt numFmtId="168" formatCode="h:mm tt"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -237,12 +240,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF17365d"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -350,7 +347,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -445,7 +442,7 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
@@ -487,9 +484,6 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -502,7 +496,13 @@
     <xf xfId="0" numFmtId="168" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="168" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
@@ -530,7 +530,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -837,17 +837,17 @@
   <dimension ref="A1:K134"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="55" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="56" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="57" width="28.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="57" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="58" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="58" width="15.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="59" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="59" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="59" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="60" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="60" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="56" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="57" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="58" width="28.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="58" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="59" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="59" width="15.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="60" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="60" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="60" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="61" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="61" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="30">
@@ -1037,15 +1037,15 @@
       <c r="I10" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="8">
         <f>IF($B$8="","",$B$8+0)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B11" s="47">
+      <c r="B11" s="46">
         <f>IF(A11="","",TEXT(A11,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
@@ -1055,11 +1055,11 @@
       <c r="D11" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="48">
-        <v>3.832986111111111</v>
-      </c>
-      <c r="F11" s="49">
-        <v>3.874652777777778</v>
+      <c r="E11" s="47">
+        <v>4.832870370370371</v>
+      </c>
+      <c r="F11" s="48">
+        <v>4.874537037037037</v>
       </c>
       <c r="G11" s="10">
         <f>IF(D11="P",1,0)</f>
@@ -1078,7 +1078,7 @@
         <f>IF($B$8="","",$B$8+1)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B12" s="47">
+      <c r="B12" s="46">
         <f>IF(A12="","",TEXT(A12,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
@@ -1088,11 +1088,11 @@
       <c r="D12" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="48">
-        <v>3.874652777777778</v>
-      </c>
-      <c r="F12" s="49">
-        <v>3.9163194444444445</v>
+      <c r="E12" s="47">
+        <v>4.874537037037037</v>
+      </c>
+      <c r="F12" s="48">
+        <v>4.916203703703704</v>
       </c>
       <c r="G12" s="10">
         <f>IF(D12="P",1,0)</f>
@@ -1111,7 +1111,7 @@
         <f>IF($B$8="","",$B$8+2)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B13" s="47">
+      <c r="B13" s="46">
         <f>IF(A13="","",TEXT(A13,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
@@ -1121,10 +1121,10 @@
       <c r="D13" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="48">
+      <c r="E13" s="47">
         <v>46023.875</v>
       </c>
-      <c r="F13" s="49">
+      <c r="F13" s="48">
         <v>46023.916666666664</v>
       </c>
       <c r="G13" s="10">
@@ -1144,7 +1144,7 @@
         <f>IF($B$8="","",$B$8+3)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B14" s="47">
+      <c r="B14" s="46">
         <f>IF(A14="","",TEXT(A14,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
@@ -1152,12 +1152,12 @@
         <v>46</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="E14" s="50" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="49" t="s">
+      <c r="F14" s="50" t="s">
         <v>46</v>
       </c>
       <c r="G14" s="10">
@@ -1177,20 +1177,20 @@
         <f>IF($B$8="","",$B$8+4)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B15" s="47">
+      <c r="B15" s="46">
         <f>IF(A15="","",TEXT(A15,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C15" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" s="48" t="s">
+      <c r="E15" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="49" t="s">
+      <c r="F15" s="50" t="s">
         <v>46</v>
       </c>
       <c r="G15" s="10">
@@ -1210,7 +1210,7 @@
         <f>IF($B$8="","",$B$8+5)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B16" s="47">
+      <c r="B16" s="46">
         <f>IF(A16="","",TEXT(A16,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
@@ -1220,10 +1220,10 @@
       <c r="D16" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="48">
+      <c r="E16" s="47">
         <v>46023.791666666664</v>
       </c>
-      <c r="F16" s="49">
+      <c r="F16" s="48">
         <v>46023.833333333336</v>
       </c>
       <c r="G16" s="10">
@@ -1243,14 +1243,22 @@
         <f>IF($B$8="","",$B$8+6)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B17" s="47">
+      <c r="B17" s="46">
         <f>IF(A17="","",TEXT(A17,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="49"/>
+      <c r="C17" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="47">
+        <v>46023.791666666664</v>
+      </c>
+      <c r="F17" s="48">
+        <v>46023.833333333336</v>
+      </c>
       <c r="G17" s="10">
         <f>IF(D17="P",1,0)</f>
       </c>
@@ -1268,14 +1276,14 @@
         <f>IF($B$8="","",$B$8+7)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B18" s="47">
+      <c r="B18" s="46">
         <f>IF(A18="","",TEXT(A18,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C18" s="36"/>
       <c r="D18" s="21"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="49"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="48"/>
       <c r="G18" s="10">
         <f>IF(D18="P",1,0)</f>
       </c>
@@ -1293,14 +1301,14 @@
         <f>IF($B$8="","",$B$8+8)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B19" s="47">
+      <c r="B19" s="46">
         <f>IF(A19="","",TEXT(A19,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C19" s="36"/>
       <c r="D19" s="21"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="49"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="48"/>
       <c r="G19" s="10">
         <f>IF(D19="P",1,0)</f>
       </c>
@@ -1318,14 +1326,14 @@
         <f>IF($B$8="","",$B$8+9)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B20" s="47">
+      <c r="B20" s="46">
         <f>IF(A20="","",TEXT(A20,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C20" s="36"/>
       <c r="D20" s="21"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="49"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="48"/>
       <c r="G20" s="10">
         <f>IF(D20="P",1,0)</f>
       </c>
@@ -1343,14 +1351,14 @@
         <f>IF($B$8="","",$B$8+10)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B21" s="47">
+      <c r="B21" s="46">
         <f>IF(A21="","",TEXT(A21,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C21" s="36"/>
       <c r="D21" s="21"/>
-      <c r="E21" s="48"/>
-      <c r="F21" s="49"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="48"/>
       <c r="G21" s="10">
         <f>IF(D21="P",1,0)</f>
       </c>
@@ -1368,14 +1376,14 @@
         <f>IF($B$8="","",$B$8+11)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B22" s="47">
+      <c r="B22" s="46">
         <f>IF(A22="","",TEXT(A22,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C22" s="36"/>
       <c r="D22" s="21"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="49"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="48"/>
       <c r="G22" s="10">
         <f>IF(D22="P",1,0)</f>
       </c>
@@ -1393,14 +1401,14 @@
         <f>IF($B$8="","",$B$8+12)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B23" s="47">
+      <c r="B23" s="46">
         <f>IF(A23="","",TEXT(A23,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C23" s="36"/>
       <c r="D23" s="21"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="49"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="48"/>
       <c r="G23" s="10">
         <f>IF(D23="P",1,0)</f>
       </c>
@@ -1418,14 +1426,14 @@
         <f>IF($B$8="","",$B$8+13)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B24" s="47">
+      <c r="B24" s="46">
         <f>IF(A24="","",TEXT(A24,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C24" s="36"/>
       <c r="D24" s="21"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="49"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="48"/>
       <c r="G24" s="10">
         <f>IF(D24="P",1,0)</f>
       </c>
@@ -1443,14 +1451,14 @@
         <f>IF($B$8="","",$B$8+14)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B25" s="47">
+      <c r="B25" s="46">
         <f>IF(A25="","",TEXT(A25,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C25" s="36"/>
       <c r="D25" s="21"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="49"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="48"/>
       <c r="G25" s="10">
         <f>IF(D25="P",1,0)</f>
       </c>
@@ -1468,14 +1476,14 @@
         <f>IF($B$8="","",$B$8+15)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B26" s="47">
+      <c r="B26" s="46">
         <f>IF(A26="","",TEXT(A26,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C26" s="36"/>
       <c r="D26" s="21"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="49"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="48"/>
       <c r="G26" s="10">
         <f>IF(D26="P",1,0)</f>
       </c>
@@ -1493,14 +1501,14 @@
         <f>IF($B$8="","",$B$8+16)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B27" s="47">
+      <c r="B27" s="46">
         <f>IF(A27="","",TEXT(A27,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C27" s="36"/>
       <c r="D27" s="21"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="49"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="48"/>
       <c r="G27" s="10">
         <f>IF(D27="P",1,0)</f>
       </c>
@@ -1518,14 +1526,14 @@
         <f>IF($B$8="","",$B$8+17)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B28" s="47">
+      <c r="B28" s="46">
         <f>IF(A28="","",TEXT(A28,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C28" s="36"/>
       <c r="D28" s="21"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="49"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="48"/>
       <c r="G28" s="10">
         <f>IF(D28="P",1,0)</f>
       </c>
@@ -1543,14 +1551,14 @@
         <f>IF($B$8="","",$B$8+18)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B29" s="47">
+      <c r="B29" s="46">
         <f>IF(A29="","",TEXT(A29,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C29" s="36"/>
       <c r="D29" s="21"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="49"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="48"/>
       <c r="G29" s="10">
         <f>IF(D29="P",1,0)</f>
       </c>
@@ -1568,14 +1576,14 @@
         <f>IF($B$8="","",$B$8+19)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B30" s="47">
+      <c r="B30" s="46">
         <f>IF(A30="","",TEXT(A30,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C30" s="36"/>
       <c r="D30" s="21"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="49"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="48"/>
       <c r="G30" s="10">
         <f>IF(D30="P",1,0)</f>
       </c>
@@ -1593,14 +1601,14 @@
         <f>IF($B$8="","",$B$8+20)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B31" s="47">
+      <c r="B31" s="46">
         <f>IF(A31="","",TEXT(A31,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C31" s="36"/>
       <c r="D31" s="21"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="49"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="48"/>
       <c r="G31" s="10">
         <f>IF(D31="P",1,0)</f>
       </c>
@@ -1618,14 +1626,14 @@
         <f>IF($B$8="","",$B$8+21)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B32" s="47">
+      <c r="B32" s="46">
         <f>IF(A32="","",TEXT(A32,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C32" s="36"/>
       <c r="D32" s="21"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="49"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="48"/>
       <c r="G32" s="10">
         <f>IF(D32="P",1,0)</f>
       </c>
@@ -1643,14 +1651,14 @@
         <f>IF($B$8="","",$B$8+22)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B33" s="47">
+      <c r="B33" s="46">
         <f>IF(A33="","",TEXT(A33,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C33" s="36"/>
       <c r="D33" s="21"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="49"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="48"/>
       <c r="G33" s="10">
         <f>IF(D33="P",1,0)</f>
       </c>
@@ -1668,14 +1676,14 @@
         <f>IF($B$8="","",$B$8+23)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B34" s="47">
+      <c r="B34" s="46">
         <f>IF(A34="","",TEXT(A34,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C34" s="36"/>
       <c r="D34" s="21"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="49"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="48"/>
       <c r="G34" s="10">
         <f>IF(D34="P",1,0)</f>
       </c>
@@ -1693,14 +1701,14 @@
         <f>IF($B$8="","",$B$8+24)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B35" s="47">
+      <c r="B35" s="46">
         <f>IF(A35="","",TEXT(A35,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C35" s="36"/>
       <c r="D35" s="21"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="49"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="48"/>
       <c r="G35" s="10">
         <f>IF(D35="P",1,0)</f>
       </c>
@@ -1718,14 +1726,14 @@
         <f>IF($B$8="","",$B$8+25)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B36" s="47">
+      <c r="B36" s="46">
         <f>IF(A36="","",TEXT(A36,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C36" s="36"/>
       <c r="D36" s="21"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="49"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="48"/>
       <c r="G36" s="10">
         <f>IF(D36="P",1,0)</f>
       </c>
@@ -1743,14 +1751,14 @@
         <f>IF($B$8="","",$B$8+26)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B37" s="47">
+      <c r="B37" s="46">
         <f>IF(A37="","",TEXT(A37,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C37" s="36"/>
       <c r="D37" s="21"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="49"/>
+      <c r="E37" s="47"/>
+      <c r="F37" s="48"/>
       <c r="G37" s="10">
         <f>IF(D37="P",1,0)</f>
       </c>
@@ -1768,14 +1776,14 @@
         <f>IF($B$8="","",$B$8+27)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B38" s="47">
+      <c r="B38" s="46">
         <f>IF(A38="","",TEXT(A38,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C38" s="36"/>
       <c r="D38" s="21"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="49"/>
+      <c r="E38" s="47"/>
+      <c r="F38" s="48"/>
       <c r="G38" s="10">
         <f>IF(D38="P",1,0)</f>
       </c>
@@ -1793,14 +1801,14 @@
         <f>IF($B$8="","",$B$8+28)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B39" s="47">
+      <c r="B39" s="46">
         <f>IF(A39="","",TEXT(A39,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C39" s="36"/>
       <c r="D39" s="21"/>
-      <c r="E39" s="48"/>
-      <c r="F39" s="49"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="48"/>
       <c r="G39" s="10">
         <f>IF(D39="P",1,0)</f>
       </c>
@@ -1818,14 +1826,14 @@
         <f>IF($B$8="","",$B$8+29)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B40" s="47">
+      <c r="B40" s="46">
         <f>IF(A40="","",TEXT(A40,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C40" s="36"/>
       <c r="D40" s="21"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="49"/>
+      <c r="E40" s="47"/>
+      <c r="F40" s="48"/>
       <c r="G40" s="10">
         <f>IF(D40="P",1,0)</f>
       </c>
@@ -1843,14 +1851,14 @@
         <f>IF($B$8="","",$B$8+30)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B41" s="47">
+      <c r="B41" s="46">
         <f>IF(A41="","",TEXT(A41,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C41" s="36"/>
       <c r="D41" s="21"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="49"/>
+      <c r="E41" s="47"/>
+      <c r="F41" s="48"/>
       <c r="G41" s="10">
         <f>IF(D41="P",1,0)</f>
       </c>
@@ -1868,14 +1876,14 @@
         <f>IF($B$8="","",$B$8+31)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B42" s="47">
+      <c r="B42" s="46">
         <f>IF(A42="","",TEXT(A42,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C42" s="36"/>
       <c r="D42" s="21"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="49"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="48"/>
       <c r="G42" s="10">
         <f>IF(D42="P",1,0)</f>
       </c>
@@ -1893,14 +1901,14 @@
         <f>IF($B$8="","",$B$8+32)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B43" s="47">
+      <c r="B43" s="46">
         <f>IF(A43="","",TEXT(A43,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C43" s="36"/>
       <c r="D43" s="21"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="49"/>
+      <c r="E43" s="47"/>
+      <c r="F43" s="48"/>
       <c r="G43" s="10">
         <f>IF(D43="P",1,0)</f>
       </c>
@@ -1918,14 +1926,14 @@
         <f>IF($B$8="","",$B$8+33)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B44" s="47">
+      <c r="B44" s="46">
         <f>IF(A44="","",TEXT(A44,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C44" s="36"/>
       <c r="D44" s="21"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="49"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="48"/>
       <c r="G44" s="10">
         <f>IF(D44="P",1,0)</f>
       </c>
@@ -1943,14 +1951,14 @@
         <f>IF($B$8="","",$B$8+34)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B45" s="47">
+      <c r="B45" s="46">
         <f>IF(A45="","",TEXT(A45,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C45" s="36"/>
       <c r="D45" s="21"/>
-      <c r="E45" s="48"/>
-      <c r="F45" s="49"/>
+      <c r="E45" s="47"/>
+      <c r="F45" s="48"/>
       <c r="G45" s="10">
         <f>IF(D45="P",1,0)</f>
       </c>
@@ -1968,14 +1976,14 @@
         <f>IF($B$8="","",$B$8+35)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B46" s="47">
+      <c r="B46" s="46">
         <f>IF(A46="","",TEXT(A46,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C46" s="36"/>
       <c r="D46" s="21"/>
-      <c r="E46" s="48"/>
-      <c r="F46" s="49"/>
+      <c r="E46" s="47"/>
+      <c r="F46" s="48"/>
       <c r="G46" s="10">
         <f>IF(D46="P",1,0)</f>
       </c>
@@ -1993,14 +2001,14 @@
         <f>IF($B$8="","",$B$8+36)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B47" s="47">
+      <c r="B47" s="46">
         <f>IF(A47="","",TEXT(A47,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C47" s="36"/>
       <c r="D47" s="21"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="49"/>
+      <c r="E47" s="47"/>
+      <c r="F47" s="48"/>
       <c r="G47" s="10">
         <f>IF(D47="P",1,0)</f>
       </c>
@@ -2018,14 +2026,14 @@
         <f>IF($B$8="","",$B$8+37)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B48" s="47">
+      <c r="B48" s="46">
         <f>IF(A48="","",TEXT(A48,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C48" s="36"/>
       <c r="D48" s="21"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="49"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="48"/>
       <c r="G48" s="10">
         <f>IF(D48="P",1,0)</f>
       </c>
@@ -2043,14 +2051,14 @@
         <f>IF($B$8="","",$B$8+38)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B49" s="47">
+      <c r="B49" s="46">
         <f>IF(A49="","",TEXT(A49,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C49" s="36"/>
       <c r="D49" s="21"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="49"/>
+      <c r="E49" s="47"/>
+      <c r="F49" s="48"/>
       <c r="G49" s="10">
         <f>IF(D49="P",1,0)</f>
       </c>
@@ -2068,14 +2076,14 @@
         <f>IF($B$8="","",$B$8+39)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B50" s="47">
+      <c r="B50" s="46">
         <f>IF(A50="","",TEXT(A50,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C50" s="36"/>
       <c r="D50" s="21"/>
-      <c r="E50" s="48"/>
-      <c r="F50" s="49"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="48"/>
       <c r="G50" s="10">
         <f>IF(D50="P",1,0)</f>
       </c>
@@ -2093,14 +2101,14 @@
         <f>IF($B$8="","",$B$8+40)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B51" s="47">
+      <c r="B51" s="46">
         <f>IF(A51="","",TEXT(A51,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C51" s="36"/>
       <c r="D51" s="21"/>
-      <c r="E51" s="48"/>
-      <c r="F51" s="49"/>
+      <c r="E51" s="47"/>
+      <c r="F51" s="48"/>
       <c r="G51" s="10">
         <f>IF(D51="P",1,0)</f>
       </c>
@@ -2118,14 +2126,14 @@
         <f>IF($B$8="","",$B$8+41)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B52" s="47">
+      <c r="B52" s="46">
         <f>IF(A52="","",TEXT(A52,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C52" s="36"/>
       <c r="D52" s="21"/>
-      <c r="E52" s="48"/>
-      <c r="F52" s="49"/>
+      <c r="E52" s="47"/>
+      <c r="F52" s="48"/>
       <c r="G52" s="10">
         <f>IF(D52="P",1,0)</f>
       </c>
@@ -2143,14 +2151,14 @@
         <f>IF($B$8="","",$B$8+42)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B53" s="47">
+      <c r="B53" s="46">
         <f>IF(A53="","",TEXT(A53,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C53" s="36"/>
       <c r="D53" s="21"/>
-      <c r="E53" s="48"/>
-      <c r="F53" s="49"/>
+      <c r="E53" s="47"/>
+      <c r="F53" s="48"/>
       <c r="G53" s="10">
         <f>IF(D53="P",1,0)</f>
       </c>
@@ -2168,14 +2176,14 @@
         <f>IF($B$8="","",$B$8+43)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B54" s="47">
+      <c r="B54" s="46">
         <f>IF(A54="","",TEXT(A54,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C54" s="36"/>
       <c r="D54" s="21"/>
-      <c r="E54" s="48"/>
-      <c r="F54" s="49"/>
+      <c r="E54" s="47"/>
+      <c r="F54" s="48"/>
       <c r="G54" s="10">
         <f>IF(D54="P",1,0)</f>
       </c>
@@ -2193,14 +2201,14 @@
         <f>IF($B$8="","",$B$8+44)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B55" s="47">
+      <c r="B55" s="46">
         <f>IF(A55="","",TEXT(A55,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C55" s="36"/>
       <c r="D55" s="21"/>
-      <c r="E55" s="48"/>
-      <c r="F55" s="49"/>
+      <c r="E55" s="47"/>
+      <c r="F55" s="48"/>
       <c r="G55" s="10">
         <f>IF(D55="P",1,0)</f>
       </c>
@@ -2218,14 +2226,14 @@
         <f>IF($B$8="","",$B$8+45)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B56" s="47">
+      <c r="B56" s="46">
         <f>IF(A56="","",TEXT(A56,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C56" s="36"/>
       <c r="D56" s="21"/>
-      <c r="E56" s="48"/>
-      <c r="F56" s="49"/>
+      <c r="E56" s="47"/>
+      <c r="F56" s="48"/>
       <c r="G56" s="10">
         <f>IF(D56="P",1,0)</f>
       </c>
@@ -2243,14 +2251,14 @@
         <f>IF($B$8="","",$B$8+46)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B57" s="47">
+      <c r="B57" s="46">
         <f>IF(A57="","",TEXT(A57,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C57" s="36"/>
       <c r="D57" s="21"/>
-      <c r="E57" s="48"/>
-      <c r="F57" s="49"/>
+      <c r="E57" s="47"/>
+      <c r="F57" s="48"/>
       <c r="G57" s="10">
         <f>IF(D57="P",1,0)</f>
       </c>
@@ -2268,14 +2276,14 @@
         <f>IF($B$8="","",$B$8+47)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B58" s="47">
+      <c r="B58" s="46">
         <f>IF(A58="","",TEXT(A58,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C58" s="36"/>
       <c r="D58" s="21"/>
-      <c r="E58" s="48"/>
-      <c r="F58" s="49"/>
+      <c r="E58" s="47"/>
+      <c r="F58" s="48"/>
       <c r="G58" s="10">
         <f>IF(D58="P",1,0)</f>
       </c>
@@ -2293,14 +2301,14 @@
         <f>IF($B$8="","",$B$8+48)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B59" s="47">
+      <c r="B59" s="46">
         <f>IF(A59="","",TEXT(A59,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C59" s="36"/>
       <c r="D59" s="21"/>
-      <c r="E59" s="48"/>
-      <c r="F59" s="49"/>
+      <c r="E59" s="47"/>
+      <c r="F59" s="48"/>
       <c r="G59" s="10">
         <f>IF(D59="P",1,0)</f>
       </c>
@@ -2318,14 +2326,14 @@
         <f>IF($B$8="","",$B$8+49)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B60" s="47">
+      <c r="B60" s="46">
         <f>IF(A60="","",TEXT(A60,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C60" s="36"/>
       <c r="D60" s="21"/>
-      <c r="E60" s="48"/>
-      <c r="F60" s="49"/>
+      <c r="E60" s="47"/>
+      <c r="F60" s="48"/>
       <c r="G60" s="10">
         <f>IF(D60="P",1,0)</f>
       </c>
@@ -2343,14 +2351,14 @@
         <f>IF($B$8="","",$B$8+50)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B61" s="47">
+      <c r="B61" s="46">
         <f>IF(A61="","",TEXT(A61,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C61" s="36"/>
       <c r="D61" s="21"/>
-      <c r="E61" s="48"/>
-      <c r="F61" s="49"/>
+      <c r="E61" s="47"/>
+      <c r="F61" s="48"/>
       <c r="G61" s="10">
         <f>IF(D61="P",1,0)</f>
       </c>
@@ -2368,14 +2376,14 @@
         <f>IF($B$8="","",$B$8+51)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B62" s="47">
+      <c r="B62" s="46">
         <f>IF(A62="","",TEXT(A62,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C62" s="36"/>
       <c r="D62" s="21"/>
-      <c r="E62" s="48"/>
-      <c r="F62" s="49"/>
+      <c r="E62" s="47"/>
+      <c r="F62" s="48"/>
       <c r="G62" s="10">
         <f>IF(D62="P",1,0)</f>
       </c>
@@ -2393,14 +2401,14 @@
         <f>IF($B$8="","",$B$8+52)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B63" s="47">
+      <c r="B63" s="46">
         <f>IF(A63="","",TEXT(A63,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C63" s="36"/>
       <c r="D63" s="21"/>
-      <c r="E63" s="48"/>
-      <c r="F63" s="49"/>
+      <c r="E63" s="47"/>
+      <c r="F63" s="48"/>
       <c r="G63" s="10">
         <f>IF(D63="P",1,0)</f>
       </c>
@@ -2418,14 +2426,14 @@
         <f>IF($B$8="","",$B$8+53)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B64" s="47">
+      <c r="B64" s="46">
         <f>IF(A64="","",TEXT(A64,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C64" s="36"/>
       <c r="D64" s="21"/>
-      <c r="E64" s="48"/>
-      <c r="F64" s="49"/>
+      <c r="E64" s="47"/>
+      <c r="F64" s="48"/>
       <c r="G64" s="10">
         <f>IF(D64="P",1,0)</f>
       </c>
@@ -2443,14 +2451,14 @@
         <f>IF($B$8="","",$B$8+54)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B65" s="47">
+      <c r="B65" s="46">
         <f>IF(A65="","",TEXT(A65,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C65" s="36"/>
       <c r="D65" s="21"/>
-      <c r="E65" s="48"/>
-      <c r="F65" s="49"/>
+      <c r="E65" s="47"/>
+      <c r="F65" s="48"/>
       <c r="G65" s="10">
         <f>IF(D65="P",1,0)</f>
       </c>
@@ -2468,14 +2476,14 @@
         <f>IF($B$8="","",$B$8+55)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B66" s="47">
+      <c r="B66" s="46">
         <f>IF(A66="","",TEXT(A66,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C66" s="36"/>
       <c r="D66" s="21"/>
-      <c r="E66" s="48"/>
-      <c r="F66" s="49"/>
+      <c r="E66" s="47"/>
+      <c r="F66" s="48"/>
       <c r="G66" s="10">
         <f>IF(D66="P",1,0)</f>
       </c>
@@ -2493,14 +2501,14 @@
         <f>IF($B$8="","",$B$8+56)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B67" s="47">
+      <c r="B67" s="46">
         <f>IF(A67="","",TEXT(A67,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C67" s="36"/>
       <c r="D67" s="21"/>
-      <c r="E67" s="48"/>
-      <c r="F67" s="49"/>
+      <c r="E67" s="47"/>
+      <c r="F67" s="48"/>
       <c r="G67" s="10">
         <f>IF(D67="P",1,0)</f>
       </c>
@@ -2518,14 +2526,14 @@
         <f>IF($B$8="","",$B$8+57)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B68" s="47">
+      <c r="B68" s="46">
         <f>IF(A68="","",TEXT(A68,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C68" s="36"/>
       <c r="D68" s="21"/>
-      <c r="E68" s="48"/>
-      <c r="F68" s="49"/>
+      <c r="E68" s="47"/>
+      <c r="F68" s="48"/>
       <c r="G68" s="10">
         <f>IF(D68="P",1,0)</f>
       </c>
@@ -2543,14 +2551,14 @@
         <f>IF($B$8="","",$B$8+58)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B69" s="47">
+      <c r="B69" s="46">
         <f>IF(A69="","",TEXT(A69,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C69" s="36"/>
       <c r="D69" s="21"/>
-      <c r="E69" s="48"/>
-      <c r="F69" s="49"/>
+      <c r="E69" s="47"/>
+      <c r="F69" s="48"/>
       <c r="G69" s="10">
         <f>IF(D69="P",1,0)</f>
       </c>
@@ -2568,14 +2576,14 @@
         <f>IF($B$8="","",$B$8+59)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B70" s="47">
+      <c r="B70" s="46">
         <f>IF(A70="","",TEXT(A70,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C70" s="36"/>
       <c r="D70" s="21"/>
-      <c r="E70" s="48"/>
-      <c r="F70" s="49"/>
+      <c r="E70" s="47"/>
+      <c r="F70" s="48"/>
       <c r="G70" s="10">
         <f>IF(D70="P",1,0)</f>
       </c>
@@ -2593,14 +2601,14 @@
         <f>IF($B$8="","",$B$8+60)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B71" s="47">
+      <c r="B71" s="46">
         <f>IF(A71="","",TEXT(A71,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C71" s="36"/>
       <c r="D71" s="21"/>
-      <c r="E71" s="48"/>
-      <c r="F71" s="49"/>
+      <c r="E71" s="47"/>
+      <c r="F71" s="48"/>
       <c r="G71" s="10">
         <f>IF(D71="P",1,0)</f>
       </c>
@@ -2618,14 +2626,14 @@
         <f>IF($B$8="","",$B$8+61)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B72" s="47">
+      <c r="B72" s="46">
         <f>IF(A72="","",TEXT(A72,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C72" s="36"/>
       <c r="D72" s="21"/>
-      <c r="E72" s="48"/>
-      <c r="F72" s="49"/>
+      <c r="E72" s="47"/>
+      <c r="F72" s="48"/>
       <c r="G72" s="10">
         <f>IF(D72="P",1,0)</f>
       </c>
@@ -2643,14 +2651,14 @@
         <f>IF($B$8="","",$B$8+62)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B73" s="47">
+      <c r="B73" s="46">
         <f>IF(A73="","",TEXT(A73,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C73" s="36"/>
       <c r="D73" s="21"/>
-      <c r="E73" s="48"/>
-      <c r="F73" s="49"/>
+      <c r="E73" s="47"/>
+      <c r="F73" s="48"/>
       <c r="G73" s="10">
         <f>IF(D73="P",1,0)</f>
       </c>
@@ -2668,14 +2676,14 @@
         <f>IF($B$8="","",$B$8+63)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B74" s="47">
+      <c r="B74" s="46">
         <f>IF(A74="","",TEXT(A74,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C74" s="36"/>
       <c r="D74" s="21"/>
-      <c r="E74" s="48"/>
-      <c r="F74" s="49"/>
+      <c r="E74" s="47"/>
+      <c r="F74" s="48"/>
       <c r="G74" s="10">
         <f>IF(D74="P",1,0)</f>
       </c>
@@ -2693,14 +2701,14 @@
         <f>IF($B$8="","",$B$8+64)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B75" s="47">
+      <c r="B75" s="46">
         <f>IF(A75="","",TEXT(A75,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C75" s="36"/>
       <c r="D75" s="21"/>
-      <c r="E75" s="48"/>
-      <c r="F75" s="49"/>
+      <c r="E75" s="47"/>
+      <c r="F75" s="48"/>
       <c r="G75" s="10">
         <f>IF(D75="P",1,0)</f>
       </c>
@@ -2718,14 +2726,14 @@
         <f>IF($B$8="","",$B$8+65)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B76" s="47">
+      <c r="B76" s="46">
         <f>IF(A76="","",TEXT(A76,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C76" s="36"/>
       <c r="D76" s="21"/>
-      <c r="E76" s="48"/>
-      <c r="F76" s="49"/>
+      <c r="E76" s="47"/>
+      <c r="F76" s="48"/>
       <c r="G76" s="10">
         <f>IF(D76="P",1,0)</f>
       </c>
@@ -2743,14 +2751,14 @@
         <f>IF($B$8="","",$B$8+66)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B77" s="47">
+      <c r="B77" s="46">
         <f>IF(A77="","",TEXT(A77,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C77" s="36"/>
       <c r="D77" s="21"/>
-      <c r="E77" s="48"/>
-      <c r="F77" s="49"/>
+      <c r="E77" s="47"/>
+      <c r="F77" s="48"/>
       <c r="G77" s="10">
         <f>IF(D77="P",1,0)</f>
       </c>
@@ -2768,14 +2776,14 @@
         <f>IF($B$8="","",$B$8+67)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B78" s="47">
+      <c r="B78" s="46">
         <f>IF(A78="","",TEXT(A78,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C78" s="36"/>
       <c r="D78" s="21"/>
-      <c r="E78" s="48"/>
-      <c r="F78" s="49"/>
+      <c r="E78" s="47"/>
+      <c r="F78" s="48"/>
       <c r="G78" s="10">
         <f>IF(D78="P",1,0)</f>
       </c>
@@ -2793,14 +2801,14 @@
         <f>IF($B$8="","",$B$8+68)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B79" s="47">
+      <c r="B79" s="46">
         <f>IF(A79="","",TEXT(A79,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C79" s="36"/>
       <c r="D79" s="21"/>
-      <c r="E79" s="48"/>
-      <c r="F79" s="49"/>
+      <c r="E79" s="47"/>
+      <c r="F79" s="48"/>
       <c r="G79" s="10">
         <f>IF(D79="P",1,0)</f>
       </c>
@@ -2818,14 +2826,14 @@
         <f>IF($B$8="","",$B$8+69)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B80" s="47">
+      <c r="B80" s="46">
         <f>IF(A80="","",TEXT(A80,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C80" s="36"/>
       <c r="D80" s="21"/>
-      <c r="E80" s="48"/>
-      <c r="F80" s="49"/>
+      <c r="E80" s="47"/>
+      <c r="F80" s="48"/>
       <c r="G80" s="10">
         <f>IF(D80="P",1,0)</f>
       </c>
@@ -2843,14 +2851,14 @@
         <f>IF($B$8="","",$B$8+70)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B81" s="47">
+      <c r="B81" s="46">
         <f>IF(A81="","",TEXT(A81,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C81" s="36"/>
       <c r="D81" s="21"/>
-      <c r="E81" s="48"/>
-      <c r="F81" s="49"/>
+      <c r="E81" s="47"/>
+      <c r="F81" s="48"/>
       <c r="G81" s="10">
         <f>IF(D81="P",1,0)</f>
       </c>
@@ -2868,14 +2876,14 @@
         <f>IF($B$8="","",$B$8+71)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B82" s="47">
+      <c r="B82" s="46">
         <f>IF(A82="","",TEXT(A82,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C82" s="36"/>
       <c r="D82" s="21"/>
-      <c r="E82" s="48"/>
-      <c r="F82" s="49"/>
+      <c r="E82" s="47"/>
+      <c r="F82" s="48"/>
       <c r="G82" s="10">
         <f>IF(D82="P",1,0)</f>
       </c>
@@ -2893,14 +2901,14 @@
         <f>IF($B$8="","",$B$8+72)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B83" s="47">
+      <c r="B83" s="46">
         <f>IF(A83="","",TEXT(A83,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C83" s="36"/>
       <c r="D83" s="21"/>
-      <c r="E83" s="48"/>
-      <c r="F83" s="49"/>
+      <c r="E83" s="47"/>
+      <c r="F83" s="48"/>
       <c r="G83" s="10">
         <f>IF(D83="P",1,0)</f>
       </c>
@@ -2918,14 +2926,14 @@
         <f>IF($B$8="","",$B$8+73)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B84" s="47">
+      <c r="B84" s="46">
         <f>IF(A84="","",TEXT(A84,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C84" s="36"/>
       <c r="D84" s="21"/>
-      <c r="E84" s="48"/>
-      <c r="F84" s="49"/>
+      <c r="E84" s="47"/>
+      <c r="F84" s="48"/>
       <c r="G84" s="10">
         <f>IF(D84="P",1,0)</f>
       </c>
@@ -2943,14 +2951,14 @@
         <f>IF($B$8="","",$B$8+74)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B85" s="47">
+      <c r="B85" s="46">
         <f>IF(A85="","",TEXT(A85,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C85" s="36"/>
       <c r="D85" s="21"/>
-      <c r="E85" s="48"/>
-      <c r="F85" s="49"/>
+      <c r="E85" s="47"/>
+      <c r="F85" s="48"/>
       <c r="G85" s="10">
         <f>IF(D85="P",1,0)</f>
       </c>
@@ -2968,14 +2976,14 @@
         <f>IF($B$8="","",$B$8+75)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B86" s="47">
+      <c r="B86" s="46">
         <f>IF(A86="","",TEXT(A86,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C86" s="36"/>
       <c r="D86" s="21"/>
-      <c r="E86" s="48"/>
-      <c r="F86" s="49"/>
+      <c r="E86" s="47"/>
+      <c r="F86" s="48"/>
       <c r="G86" s="10">
         <f>IF(D86="P",1,0)</f>
       </c>
@@ -2993,14 +3001,14 @@
         <f>IF($B$8="","",$B$8+76)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B87" s="47">
+      <c r="B87" s="46">
         <f>IF(A87="","",TEXT(A87,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C87" s="36"/>
       <c r="D87" s="21"/>
-      <c r="E87" s="48"/>
-      <c r="F87" s="49"/>
+      <c r="E87" s="47"/>
+      <c r="F87" s="48"/>
       <c r="G87" s="10">
         <f>IF(D87="P",1,0)</f>
       </c>
@@ -3018,14 +3026,14 @@
         <f>IF($B$8="","",$B$8+77)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B88" s="47">
+      <c r="B88" s="46">
         <f>IF(A88="","",TEXT(A88,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C88" s="36"/>
       <c r="D88" s="21"/>
-      <c r="E88" s="48"/>
-      <c r="F88" s="49"/>
+      <c r="E88" s="47"/>
+      <c r="F88" s="48"/>
       <c r="G88" s="10">
         <f>IF(D88="P",1,0)</f>
       </c>
@@ -3043,14 +3051,14 @@
         <f>IF($B$8="","",$B$8+78)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B89" s="47">
+      <c r="B89" s="46">
         <f>IF(A89="","",TEXT(A89,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C89" s="36"/>
       <c r="D89" s="21"/>
-      <c r="E89" s="48"/>
-      <c r="F89" s="49"/>
+      <c r="E89" s="47"/>
+      <c r="F89" s="48"/>
       <c r="G89" s="10">
         <f>IF(D89="P",1,0)</f>
       </c>
@@ -3068,14 +3076,14 @@
         <f>IF($B$8="","",$B$8+79)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B90" s="47">
+      <c r="B90" s="46">
         <f>IF(A90="","",TEXT(A90,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C90" s="36"/>
       <c r="D90" s="21"/>
-      <c r="E90" s="48"/>
-      <c r="F90" s="49"/>
+      <c r="E90" s="47"/>
+      <c r="F90" s="48"/>
       <c r="G90" s="10">
         <f>IF(D90="P",1,0)</f>
       </c>
@@ -3093,14 +3101,14 @@
         <f>IF($B$8="","",$B$8+80)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B91" s="47">
+      <c r="B91" s="46">
         <f>IF(A91="","",TEXT(A91,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C91" s="36"/>
       <c r="D91" s="21"/>
-      <c r="E91" s="48"/>
-      <c r="F91" s="49"/>
+      <c r="E91" s="47"/>
+      <c r="F91" s="48"/>
       <c r="G91" s="10">
         <f>IF(D91="P",1,0)</f>
       </c>
@@ -3118,14 +3126,14 @@
         <f>IF($B$8="","",$B$8+81)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B92" s="47">
+      <c r="B92" s="46">
         <f>IF(A92="","",TEXT(A92,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C92" s="36"/>
       <c r="D92" s="21"/>
-      <c r="E92" s="48"/>
-      <c r="F92" s="49"/>
+      <c r="E92" s="47"/>
+      <c r="F92" s="48"/>
       <c r="G92" s="10">
         <f>IF(D92="P",1,0)</f>
       </c>
@@ -3143,14 +3151,14 @@
         <f>IF($B$8="","",$B$8+82)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B93" s="47">
+      <c r="B93" s="46">
         <f>IF(A93="","",TEXT(A93,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C93" s="36"/>
       <c r="D93" s="21"/>
-      <c r="E93" s="48"/>
-      <c r="F93" s="49"/>
+      <c r="E93" s="47"/>
+      <c r="F93" s="48"/>
       <c r="G93" s="10">
         <f>IF(D93="P",1,0)</f>
       </c>
@@ -3168,14 +3176,14 @@
         <f>IF($B$8="","",$B$8+83)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B94" s="47">
+      <c r="B94" s="46">
         <f>IF(A94="","",TEXT(A94,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C94" s="36"/>
       <c r="D94" s="21"/>
-      <c r="E94" s="48"/>
-      <c r="F94" s="49"/>
+      <c r="E94" s="47"/>
+      <c r="F94" s="48"/>
       <c r="G94" s="10">
         <f>IF(D94="P",1,0)</f>
       </c>
@@ -3193,14 +3201,14 @@
         <f>IF($B$8="","",$B$8+84)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B95" s="47">
+      <c r="B95" s="46">
         <f>IF(A95="","",TEXT(A95,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C95" s="36"/>
       <c r="D95" s="21"/>
-      <c r="E95" s="48"/>
-      <c r="F95" s="49"/>
+      <c r="E95" s="47"/>
+      <c r="F95" s="48"/>
       <c r="G95" s="10">
         <f>IF(D95="P",1,0)</f>
       </c>
@@ -3218,14 +3226,14 @@
         <f>IF($B$8="","",$B$8+85)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B96" s="47">
+      <c r="B96" s="46">
         <f>IF(A96="","",TEXT(A96,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C96" s="36"/>
       <c r="D96" s="21"/>
-      <c r="E96" s="48"/>
-      <c r="F96" s="49"/>
+      <c r="E96" s="47"/>
+      <c r="F96" s="48"/>
       <c r="G96" s="10">
         <f>IF(D96="P",1,0)</f>
       </c>
@@ -3243,14 +3251,14 @@
         <f>IF($B$8="","",$B$8+86)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B97" s="47">
+      <c r="B97" s="46">
         <f>IF(A97="","",TEXT(A97,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C97" s="36"/>
       <c r="D97" s="21"/>
-      <c r="E97" s="48"/>
-      <c r="F97" s="49"/>
+      <c r="E97" s="47"/>
+      <c r="F97" s="48"/>
       <c r="G97" s="10">
         <f>IF(D97="P",1,0)</f>
       </c>
@@ -3268,14 +3276,14 @@
         <f>IF($B$8="","",$B$8+87)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B98" s="47">
+      <c r="B98" s="46">
         <f>IF(A98="","",TEXT(A98,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C98" s="36"/>
       <c r="D98" s="21"/>
-      <c r="E98" s="48"/>
-      <c r="F98" s="49"/>
+      <c r="E98" s="47"/>
+      <c r="F98" s="48"/>
       <c r="G98" s="10">
         <f>IF(D98="P",1,0)</f>
       </c>
@@ -3293,14 +3301,14 @@
         <f>IF($B$8="","",$B$8+88)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B99" s="47">
+      <c r="B99" s="46">
         <f>IF(A99="","",TEXT(A99,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C99" s="36"/>
       <c r="D99" s="21"/>
-      <c r="E99" s="48"/>
-      <c r="F99" s="49"/>
+      <c r="E99" s="47"/>
+      <c r="F99" s="48"/>
       <c r="G99" s="10">
         <f>IF(D99="P",1,0)</f>
       </c>
@@ -3318,14 +3326,14 @@
         <f>IF($B$8="","",$B$8+89)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B100" s="47">
+      <c r="B100" s="46">
         <f>IF(A100="","",TEXT(A100,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C100" s="36"/>
       <c r="D100" s="21"/>
-      <c r="E100" s="48"/>
-      <c r="F100" s="49"/>
+      <c r="E100" s="47"/>
+      <c r="F100" s="48"/>
       <c r="G100" s="10">
         <f>IF(D100="P",1,0)</f>
       </c>
@@ -3343,14 +3351,14 @@
         <f>IF($B$8="","",$B$8+90)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B101" s="47">
+      <c r="B101" s="46">
         <f>IF(A101="","",TEXT(A101,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C101" s="36"/>
       <c r="D101" s="21"/>
-      <c r="E101" s="48"/>
-      <c r="F101" s="49"/>
+      <c r="E101" s="47"/>
+      <c r="F101" s="48"/>
       <c r="G101" s="10">
         <f>IF(D101="P",1,0)</f>
       </c>
@@ -3368,14 +3376,14 @@
         <f>IF($B$8="","",$B$8+91)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B102" s="47">
+      <c r="B102" s="46">
         <f>IF(A102="","",TEXT(A102,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C102" s="36"/>
       <c r="D102" s="21"/>
-      <c r="E102" s="48"/>
-      <c r="F102" s="49"/>
+      <c r="E102" s="47"/>
+      <c r="F102" s="48"/>
       <c r="G102" s="10">
         <f>IF(D102="P",1,0)</f>
       </c>
@@ -3393,14 +3401,14 @@
         <f>IF($B$8="","",$B$8+92)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B103" s="47">
+      <c r="B103" s="46">
         <f>IF(A103="","",TEXT(A103,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C103" s="36"/>
       <c r="D103" s="21"/>
-      <c r="E103" s="48"/>
-      <c r="F103" s="49"/>
+      <c r="E103" s="47"/>
+      <c r="F103" s="48"/>
       <c r="G103" s="10">
         <f>IF(D103="P",1,0)</f>
       </c>
@@ -3418,14 +3426,14 @@
         <f>IF($B$8="","",$B$8+93)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B104" s="47">
+      <c r="B104" s="46">
         <f>IF(A104="","",TEXT(A104,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C104" s="36"/>
       <c r="D104" s="21"/>
-      <c r="E104" s="48"/>
-      <c r="F104" s="49"/>
+      <c r="E104" s="47"/>
+      <c r="F104" s="48"/>
       <c r="G104" s="10">
         <f>IF(D104="P",1,0)</f>
       </c>
@@ -3443,14 +3451,14 @@
         <f>IF($B$8="","",$B$8+94)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B105" s="47">
+      <c r="B105" s="46">
         <f>IF(A105="","",TEXT(A105,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C105" s="36"/>
       <c r="D105" s="21"/>
-      <c r="E105" s="48"/>
-      <c r="F105" s="49"/>
+      <c r="E105" s="47"/>
+      <c r="F105" s="48"/>
       <c r="G105" s="10">
         <f>IF(D105="P",1,0)</f>
       </c>
@@ -3468,14 +3476,14 @@
         <f>IF($B$8="","",$B$8+95)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B106" s="47">
+      <c r="B106" s="46">
         <f>IF(A106="","",TEXT(A106,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C106" s="36"/>
       <c r="D106" s="21"/>
-      <c r="E106" s="48"/>
-      <c r="F106" s="49"/>
+      <c r="E106" s="47"/>
+      <c r="F106" s="48"/>
       <c r="G106" s="10">
         <f>IF(D106="P",1,0)</f>
       </c>
@@ -3493,14 +3501,14 @@
         <f>IF($B$8="","",$B$8+96)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B107" s="47">
+      <c r="B107" s="46">
         <f>IF(A107="","",TEXT(A107,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C107" s="36"/>
       <c r="D107" s="21"/>
-      <c r="E107" s="48"/>
-      <c r="F107" s="49"/>
+      <c r="E107" s="47"/>
+      <c r="F107" s="48"/>
       <c r="G107" s="10">
         <f>IF(D107="P",1,0)</f>
       </c>
@@ -3518,14 +3526,14 @@
         <f>IF($B$8="","",$B$8+97)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B108" s="47">
+      <c r="B108" s="46">
         <f>IF(A108="","",TEXT(A108,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C108" s="36"/>
       <c r="D108" s="21"/>
-      <c r="E108" s="48"/>
-      <c r="F108" s="49"/>
+      <c r="E108" s="47"/>
+      <c r="F108" s="48"/>
       <c r="G108" s="10">
         <f>IF(D108="P",1,0)</f>
       </c>
@@ -3543,14 +3551,14 @@
         <f>IF($B$8="","",$B$8+98)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B109" s="47">
+      <c r="B109" s="46">
         <f>IF(A109="","",TEXT(A109,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C109" s="36"/>
       <c r="D109" s="21"/>
-      <c r="E109" s="48"/>
-      <c r="F109" s="49"/>
+      <c r="E109" s="47"/>
+      <c r="F109" s="48"/>
       <c r="G109" s="10">
         <f>IF(D109="P",1,0)</f>
       </c>
@@ -3568,14 +3576,14 @@
         <f>IF($B$8="","",$B$8+99)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B110" s="47">
+      <c r="B110" s="46">
         <f>IF(A110="","",TEXT(A110,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C110" s="36"/>
       <c r="D110" s="21"/>
-      <c r="E110" s="48"/>
-      <c r="F110" s="49"/>
+      <c r="E110" s="47"/>
+      <c r="F110" s="48"/>
       <c r="G110" s="10">
         <f>IF(D110="P",1,0)</f>
       </c>
@@ -3593,14 +3601,14 @@
         <f>IF($B$8="","",$B$8+100)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B111" s="47">
+      <c r="B111" s="46">
         <f>IF(A111="","",TEXT(A111,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C111" s="36"/>
       <c r="D111" s="21"/>
-      <c r="E111" s="48"/>
-      <c r="F111" s="49"/>
+      <c r="E111" s="47"/>
+      <c r="F111" s="48"/>
       <c r="G111" s="10">
         <f>IF(D111="P",1,0)</f>
       </c>
@@ -3618,14 +3626,14 @@
         <f>IF($B$8="","",$B$8+101)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B112" s="47">
+      <c r="B112" s="46">
         <f>IF(A112="","",TEXT(A112,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C112" s="36"/>
       <c r="D112" s="21"/>
-      <c r="E112" s="48"/>
-      <c r="F112" s="49"/>
+      <c r="E112" s="47"/>
+      <c r="F112" s="48"/>
       <c r="G112" s="10">
         <f>IF(D112="P",1,0)</f>
       </c>
@@ -3643,14 +3651,14 @@
         <f>IF($B$8="","",$B$8+102)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B113" s="47">
+      <c r="B113" s="46">
         <f>IF(A113="","",TEXT(A113,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C113" s="36"/>
       <c r="D113" s="21"/>
-      <c r="E113" s="48"/>
-      <c r="F113" s="49"/>
+      <c r="E113" s="47"/>
+      <c r="F113" s="48"/>
       <c r="G113" s="10">
         <f>IF(D113="P",1,0)</f>
       </c>
@@ -3668,14 +3676,14 @@
         <f>IF($B$8="","",$B$8+103)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B114" s="47">
+      <c r="B114" s="46">
         <f>IF(A114="","",TEXT(A114,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C114" s="36"/>
       <c r="D114" s="21"/>
-      <c r="E114" s="48"/>
-      <c r="F114" s="49"/>
+      <c r="E114" s="47"/>
+      <c r="F114" s="48"/>
       <c r="G114" s="10">
         <f>IF(D114="P",1,0)</f>
       </c>
@@ -3693,14 +3701,14 @@
         <f>IF($B$8="","",$B$8+104)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B115" s="47">
+      <c r="B115" s="46">
         <f>IF(A115="","",TEXT(A115,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C115" s="36"/>
       <c r="D115" s="21"/>
-      <c r="E115" s="48"/>
-      <c r="F115" s="49"/>
+      <c r="E115" s="47"/>
+      <c r="F115" s="48"/>
       <c r="G115" s="10">
         <f>IF(D115="P",1,0)</f>
       </c>
@@ -3718,14 +3726,14 @@
         <f>IF($B$8="","",$B$8+105)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B116" s="47">
+      <c r="B116" s="46">
         <f>IF(A116="","",TEXT(A116,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C116" s="36"/>
       <c r="D116" s="21"/>
-      <c r="E116" s="48"/>
-      <c r="F116" s="49"/>
+      <c r="E116" s="47"/>
+      <c r="F116" s="48"/>
       <c r="G116" s="10">
         <f>IF(D116="P",1,0)</f>
       </c>
@@ -3743,14 +3751,14 @@
         <f>IF($B$8="","",$B$8+106)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B117" s="47">
+      <c r="B117" s="46">
         <f>IF(A117="","",TEXT(A117,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C117" s="36"/>
       <c r="D117" s="21"/>
-      <c r="E117" s="48"/>
-      <c r="F117" s="49"/>
+      <c r="E117" s="47"/>
+      <c r="F117" s="48"/>
       <c r="G117" s="10">
         <f>IF(D117="P",1,0)</f>
       </c>
@@ -3768,14 +3776,14 @@
         <f>IF($B$8="","",$B$8+107)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B118" s="47">
+      <c r="B118" s="46">
         <f>IF(A118="","",TEXT(A118,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C118" s="36"/>
       <c r="D118" s="21"/>
-      <c r="E118" s="48"/>
-      <c r="F118" s="49"/>
+      <c r="E118" s="47"/>
+      <c r="F118" s="48"/>
       <c r="G118" s="10">
         <f>IF(D118="P",1,0)</f>
       </c>
@@ -3793,14 +3801,14 @@
         <f>IF($B$8="","",$B$8+108)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B119" s="47">
+      <c r="B119" s="46">
         <f>IF(A119="","",TEXT(A119,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C119" s="36"/>
       <c r="D119" s="21"/>
-      <c r="E119" s="48"/>
-      <c r="F119" s="49"/>
+      <c r="E119" s="47"/>
+      <c r="F119" s="48"/>
       <c r="G119" s="10">
         <f>IF(D119="P",1,0)</f>
       </c>
@@ -3818,14 +3826,14 @@
         <f>IF($B$8="","",$B$8+109)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B120" s="47">
+      <c r="B120" s="46">
         <f>IF(A120="","",TEXT(A120,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C120" s="36"/>
       <c r="D120" s="21"/>
-      <c r="E120" s="48"/>
-      <c r="F120" s="49"/>
+      <c r="E120" s="47"/>
+      <c r="F120" s="48"/>
       <c r="G120" s="10">
         <f>IF(D120="P",1,0)</f>
       </c>
@@ -3843,14 +3851,14 @@
         <f>IF($B$8="","",$B$8+110)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B121" s="47">
+      <c r="B121" s="46">
         <f>IF(A121="","",TEXT(A121,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C121" s="36"/>
       <c r="D121" s="21"/>
-      <c r="E121" s="48"/>
-      <c r="F121" s="49"/>
+      <c r="E121" s="47"/>
+      <c r="F121" s="48"/>
       <c r="G121" s="10">
         <f>IF(D121="P",1,0)</f>
       </c>
@@ -3868,14 +3876,14 @@
         <f>IF($B$8="","",$B$8+111)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B122" s="47">
+      <c r="B122" s="46">
         <f>IF(A122="","",TEXT(A122,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C122" s="36"/>
       <c r="D122" s="21"/>
-      <c r="E122" s="48"/>
-      <c r="F122" s="49"/>
+      <c r="E122" s="47"/>
+      <c r="F122" s="48"/>
       <c r="G122" s="10">
         <f>IF(D122="P",1,0)</f>
       </c>
@@ -3893,14 +3901,14 @@
         <f>IF($B$8="","",$B$8+112)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B123" s="47">
+      <c r="B123" s="46">
         <f>IF(A123="","",TEXT(A123,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C123" s="36"/>
       <c r="D123" s="21"/>
-      <c r="E123" s="48"/>
-      <c r="F123" s="49"/>
+      <c r="E123" s="47"/>
+      <c r="F123" s="48"/>
       <c r="G123" s="10">
         <f>IF(D123="P",1,0)</f>
       </c>
@@ -3918,14 +3926,14 @@
         <f>IF($B$8="","",$B$8+113)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B124" s="47">
+      <c r="B124" s="46">
         <f>IF(A124="","",TEXT(A124,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C124" s="36"/>
       <c r="D124" s="21"/>
-      <c r="E124" s="48"/>
-      <c r="F124" s="49"/>
+      <c r="E124" s="47"/>
+      <c r="F124" s="48"/>
       <c r="G124" s="10">
         <f>IF(D124="P",1,0)</f>
       </c>
@@ -3943,14 +3951,14 @@
         <f>IF($B$8="","",$B$8+114)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B125" s="47">
+      <c r="B125" s="46">
         <f>IF(A125="","",TEXT(A125,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C125" s="36"/>
       <c r="D125" s="21"/>
-      <c r="E125" s="48"/>
-      <c r="F125" s="49"/>
+      <c r="E125" s="47"/>
+      <c r="F125" s="48"/>
       <c r="G125" s="10">
         <f>IF(D125="P",1,0)</f>
       </c>
@@ -3968,14 +3976,14 @@
         <f>IF($B$8="","",$B$8+115)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B126" s="47">
+      <c r="B126" s="46">
         <f>IF(A126="","",TEXT(A126,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C126" s="36"/>
       <c r="D126" s="21"/>
-      <c r="E126" s="48"/>
-      <c r="F126" s="49"/>
+      <c r="E126" s="47"/>
+      <c r="F126" s="48"/>
       <c r="G126" s="10">
         <f>IF(D126="P",1,0)</f>
       </c>
@@ -3993,14 +4001,14 @@
         <f>IF($B$8="","",$B$8+116)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B127" s="47">
+      <c r="B127" s="46">
         <f>IF(A127="","",TEXT(A127,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C127" s="36"/>
       <c r="D127" s="21"/>
-      <c r="E127" s="48"/>
-      <c r="F127" s="49"/>
+      <c r="E127" s="47"/>
+      <c r="F127" s="48"/>
       <c r="G127" s="10">
         <f>IF(D127="P",1,0)</f>
       </c>
@@ -4018,14 +4026,14 @@
         <f>IF($B$8="","",$B$8+117)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B128" s="47">
+      <c r="B128" s="46">
         <f>IF(A128="","",TEXT(A128,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C128" s="36"/>
       <c r="D128" s="21"/>
-      <c r="E128" s="48"/>
-      <c r="F128" s="49"/>
+      <c r="E128" s="47"/>
+      <c r="F128" s="48"/>
       <c r="G128" s="10">
         <f>IF(D128="P",1,0)</f>
       </c>
@@ -4043,14 +4051,14 @@
         <f>IF($B$8="","",$B$8+118)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B129" s="47">
+      <c r="B129" s="46">
         <f>IF(A129="","",TEXT(A129,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C129" s="36"/>
       <c r="D129" s="21"/>
-      <c r="E129" s="48"/>
-      <c r="F129" s="49"/>
+      <c r="E129" s="47"/>
+      <c r="F129" s="48"/>
       <c r="G129" s="10">
         <f>IF(D129="P",1,0)</f>
       </c>
@@ -4068,14 +4076,14 @@
         <f>IF($B$8="","",$B$8+119)</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="B130" s="47">
+      <c r="B130" s="46">
         <f>IF(A130="","",TEXT(A130,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
       <c r="C130" s="36"/>
       <c r="D130" s="21"/>
-      <c r="E130" s="48"/>
-      <c r="F130" s="49"/>
+      <c r="E130" s="47"/>
+      <c r="F130" s="48"/>
       <c r="G130" s="10">
         <f>IF(D130="P",1,0)</f>
       </c>
@@ -4115,19 +4123,19 @@
       <c r="K132" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75" customFormat="1" s="40">
-      <c r="A133" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="B133" s="52"/>
-      <c r="C133" s="46"/>
-      <c r="D133" s="46"/>
-      <c r="E133" s="53"/>
-      <c r="F133" s="53"/>
-      <c r="G133" s="54"/>
-      <c r="H133" s="54"/>
-      <c r="I133" s="54"/>
-      <c r="J133" s="46"/>
-      <c r="K133" s="46"/>
+      <c r="A133" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="B133" s="53"/>
+      <c r="C133" s="32"/>
+      <c r="D133" s="32"/>
+      <c r="E133" s="54"/>
+      <c r="F133" s="54"/>
+      <c r="G133" s="55"/>
+      <c r="H133" s="55"/>
+      <c r="I133" s="55"/>
+      <c r="J133" s="32"/>
+      <c r="K133" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="18.75">
       <c r="A134" s="33"/>

--- a/MERN_Stack_4_Month_Attendance_Sheet (2).xlsx
+++ b/MERN_Stack_4_Month_Attendance_Sheet (2).xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="51">
   <si>
     <t>MERN STACK COURSE — MONTH 4 ATTENDANCE</t>
   </si>
@@ -176,9 +176,6 @@
   </si>
   <si>
     <t>_</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Introduction to HTTP and HTTPS Uses and Applications</t>
@@ -347,7 +344,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="61">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -498,9 +495,6 @@
     </xf>
     <xf xfId="0" numFmtId="168" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -837,17 +831,17 @@
   <dimension ref="A1:K134"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="56" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="57" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="58" width="28.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="58" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="59" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="59" width="15.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="60" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="60" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="60" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="61" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="61" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="55" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="56" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="57" width="28.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="57" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="58" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="58" width="15.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="59" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="59" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="59" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="60" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="60" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="30">
@@ -1056,10 +1050,10 @@
         <v>30</v>
       </c>
       <c r="E11" s="47">
-        <v>4.832870370370371</v>
+        <v>5.83275462962963</v>
       </c>
       <c r="F11" s="48">
-        <v>4.874537037037037</v>
+        <v>5.874421296296297</v>
       </c>
       <c r="G11" s="10">
         <f>IF(D11="P",1,0)</f>
@@ -1089,10 +1083,10 @@
         <v>30</v>
       </c>
       <c r="E12" s="47">
-        <v>4.874537037037037</v>
+        <v>5.874421296296297</v>
       </c>
       <c r="F12" s="48">
-        <v>4.916203703703704</v>
+        <v>5.916087962962963</v>
       </c>
       <c r="G12" s="10">
         <f>IF(D12="P",1,0)</f>
@@ -1184,9 +1178,7 @@
       <c r="C15" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="51" t="s">
-        <v>48</v>
-      </c>
+      <c r="D15" s="21"/>
       <c r="E15" s="49" t="s">
         <v>46</v>
       </c>
@@ -1215,7 +1207,7 @@
         <v>25569.229166666668</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>45</v>
@@ -1248,7 +1240,7 @@
         <v>25569.229166666668</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D17" s="21" t="s">
         <v>45</v>
@@ -1496,7 +1488,7 @@
       <c r="J26" s="32"/>
       <c r="K26" s="32"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="8">
         <f>IF($B$8="","",$B$8+16)</f>
         <v>25569.229166666668</v>
@@ -1521,7 +1513,7 @@
       <c r="J27" s="32"/>
       <c r="K27" s="32"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="8">
         <f>IF($B$8="","",$B$8+17)</f>
         <v>25569.229166666668</v>
@@ -1546,7 +1538,7 @@
       <c r="J28" s="32"/>
       <c r="K28" s="32"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="8">
         <f>IF($B$8="","",$B$8+18)</f>
         <v>25569.229166666668</v>
@@ -1571,7 +1563,7 @@
       <c r="J29" s="32"/>
       <c r="K29" s="32"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="8">
         <f>IF($B$8="","",$B$8+19)</f>
         <v>25569.229166666668</v>
@@ -1596,7 +1588,7 @@
       <c r="J30" s="32"/>
       <c r="K30" s="32"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="8">
         <f>IF($B$8="","",$B$8+20)</f>
         <v>25569.229166666668</v>
@@ -1621,7 +1613,7 @@
       <c r="J31" s="32"/>
       <c r="K31" s="32"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
       <c r="A32" s="8">
         <f>IF($B$8="","",$B$8+21)</f>
         <v>25569.229166666668</v>
@@ -1646,7 +1638,7 @@
       <c r="J32" s="32"/>
       <c r="K32" s="32"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="8">
         <f>IF($B$8="","",$B$8+22)</f>
         <v>25569.229166666668</v>
@@ -1671,7 +1663,7 @@
       <c r="J33" s="32"/>
       <c r="K33" s="32"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="8">
         <f>IF($B$8="","",$B$8+23)</f>
         <v>25569.229166666668</v>
@@ -1696,7 +1688,7 @@
       <c r="J34" s="32"/>
       <c r="K34" s="32"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="8">
         <f>IF($B$8="","",$B$8+24)</f>
         <v>25569.229166666668</v>
@@ -1721,7 +1713,7 @@
       <c r="J35" s="32"/>
       <c r="K35" s="32"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="8">
         <f>IF($B$8="","",$B$8+25)</f>
         <v>25569.229166666668</v>
@@ -4123,17 +4115,17 @@
       <c r="K132" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75" customFormat="1" s="40">
-      <c r="A133" s="52" t="s">
-        <v>51</v>
-      </c>
-      <c r="B133" s="53"/>
+      <c r="A133" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="B133" s="52"/>
       <c r="C133" s="32"/>
       <c r="D133" s="32"/>
-      <c r="E133" s="54"/>
-      <c r="F133" s="54"/>
-      <c r="G133" s="55"/>
-      <c r="H133" s="55"/>
-      <c r="I133" s="55"/>
+      <c r="E133" s="53"/>
+      <c r="F133" s="53"/>
+      <c r="G133" s="54"/>
+      <c r="H133" s="54"/>
+      <c r="I133" s="54"/>
       <c r="J133" s="32"/>
       <c r="K133" s="32"/>
     </row>

--- a/MERN_Stack_4_Month_Attendance_Sheet (2).xlsx
+++ b/MERN_Stack_4_Month_Attendance_Sheet (2).xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="52">
   <si>
     <t>MERN STACK COURSE — MONTH 4 ATTENDANCE</t>
   </si>
@@ -182,6 +182,9 @@
   </si>
   <si>
     <t xml:space="preserve">HTML tags </t>
+  </si>
+  <si>
+    <t>Tables Tag</t>
   </si>
   <si>
     <t>How to use: Enter the course start date in the yellow cell, add the topic for each class, and select P, A, or L from the Attendance dropdown. The summary updates automatically.</t>
@@ -1050,10 +1053,10 @@
         <v>30</v>
       </c>
       <c r="E11" s="47">
-        <v>5.83275462962963</v>
+        <v>6.832638888888889</v>
       </c>
       <c r="F11" s="48">
-        <v>5.874421296296297</v>
+        <v>6.874305555555556</v>
       </c>
       <c r="G11" s="10">
         <f>IF(D11="P",1,0)</f>
@@ -1083,10 +1086,10 @@
         <v>30</v>
       </c>
       <c r="E12" s="47">
-        <v>5.874421296296297</v>
+        <v>6.874305555555556</v>
       </c>
       <c r="F12" s="48">
-        <v>5.916087962962963</v>
+        <v>6.915972222222222</v>
       </c>
       <c r="G12" s="10">
         <f>IF(D12="P",1,0)</f>
@@ -1272,10 +1275,18 @@
         <f>IF(A18="","",TEXT(A18,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="C18" s="36"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="48"/>
+      <c r="C18" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="47">
+        <v>46023.875</v>
+      </c>
+      <c r="F18" s="48">
+        <v>46023.916666666664</v>
+      </c>
       <c r="G18" s="10">
         <f>IF(D18="P",1,0)</f>
       </c>
@@ -4116,7 +4127,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75" customFormat="1" s="40">
       <c r="A133" s="51" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B133" s="52"/>
       <c r="C133" s="32"/>

--- a/MERN_Stack_4_Month_Attendance_Sheet (2).xlsx
+++ b/MERN_Stack_4_Month_Attendance_Sheet (2).xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="54">
   <si>
     <t>MERN STACK COURSE — MONTH 4 ATTENDANCE</t>
   </si>
@@ -178,6 +178,9 @@
     <t>_</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>Introduction to HTTP and HTTPS Uses and Applications</t>
   </si>
   <si>
@@ -185,6 +188,9 @@
   </si>
   <si>
     <t>Tables Tag</t>
+  </si>
+  <si>
+    <t>Text Formatting Examples</t>
   </si>
   <si>
     <t>How to use: Enter the course start date in the yellow cell, add the topic for each class, and select P, A, or L from the Attendance dropdown. The summary updates automatically.</t>
@@ -347,7 +353,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -498,6 +504,9 @@
     </xf>
     <xf xfId="0" numFmtId="168" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -834,17 +843,17 @@
   <dimension ref="A1:K134"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="55" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="56" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="57" width="28.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="57" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="58" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="58" width="15.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="59" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="59" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="59" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="60" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="60" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="56" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="57" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="58" width="28.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="58" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="59" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="59" width="15.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="60" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="60" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="60" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="61" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="61" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="30">
@@ -1053,10 +1062,10 @@
         <v>30</v>
       </c>
       <c r="E11" s="47">
-        <v>6.832638888888889</v>
+        <v>46023.791666666664</v>
       </c>
       <c r="F11" s="48">
-        <v>6.874305555555556</v>
+        <v>46023.833333333336</v>
       </c>
       <c r="G11" s="10">
         <f>IF(D11="P",1,0)</f>
@@ -1086,11 +1095,9 @@
         <v>30</v>
       </c>
       <c r="E12" s="47">
-        <v>6.874305555555556</v>
-      </c>
-      <c r="F12" s="48">
-        <v>6.915972222222222</v>
-      </c>
+        <v>46023.833333333336</v>
+      </c>
+      <c r="F12" s="48"/>
       <c r="G12" s="10">
         <f>IF(D12="P",1,0)</f>
       </c>
@@ -1181,7 +1188,9 @@
       <c r="C15" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="21"/>
+      <c r="D15" s="51" t="s">
+        <v>48</v>
+      </c>
       <c r="E15" s="49" t="s">
         <v>46</v>
       </c>
@@ -1210,7 +1219,7 @@
         <v>25569.229166666668</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>45</v>
@@ -1243,7 +1252,7 @@
         <v>25569.229166666668</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" s="21" t="s">
         <v>45</v>
@@ -1276,7 +1285,7 @@
         <v>25569.229166666668</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" s="21" t="s">
         <v>45</v>
@@ -1308,9 +1317,15 @@
         <f>IF(A19="","",TEXT(A19,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="47"/>
+      <c r="C19" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="47">
+        <v>46023.875</v>
+      </c>
       <c r="F19" s="48"/>
       <c r="G19" s="10">
         <f>IF(D19="P",1,0)</f>
@@ -4126,17 +4141,17 @@
       <c r="K132" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75" customFormat="1" s="40">
-      <c r="A133" s="51" t="s">
-        <v>51</v>
-      </c>
-      <c r="B133" s="52"/>
+      <c r="A133" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="B133" s="53"/>
       <c r="C133" s="32"/>
       <c r="D133" s="32"/>
-      <c r="E133" s="53"/>
-      <c r="F133" s="53"/>
-      <c r="G133" s="54"/>
-      <c r="H133" s="54"/>
-      <c r="I133" s="54"/>
+      <c r="E133" s="54"/>
+      <c r="F133" s="54"/>
+      <c r="G133" s="55"/>
+      <c r="H133" s="55"/>
+      <c r="I133" s="55"/>
       <c r="J133" s="32"/>
       <c r="K133" s="32"/>
     </row>

--- a/MERN_Stack_4_Month_Attendance_Sheet (2).xlsx
+++ b/MERN_Stack_4_Month_Attendance_Sheet (2).xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="54">
   <si>
     <t>MERN STACK COURSE — MONTH 4 ATTENDANCE</t>
   </si>
@@ -178,9 +178,6 @@
     <t>_</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Introduction to HTTP and HTTPS Uses and Applications</t>
   </si>
   <si>
@@ -191,6 +188,9 @@
   </si>
   <si>
     <t>Text Formatting Examples</t>
+  </si>
+  <si>
+    <t>I have learned List and Links</t>
   </si>
   <si>
     <t>How to use: Enter the course start date in the yellow cell, add the topic for each class, and select P, A, or L from the Attendance dropdown. The summary updates automatically.</t>
@@ -353,7 +353,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="61">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -504,9 +504,6 @@
     </xf>
     <xf xfId="0" numFmtId="168" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -843,17 +840,17 @@
   <dimension ref="A1:K134"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="56" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="57" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="58" width="28.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="58" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="59" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="59" width="15.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="60" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="60" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="60" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="61" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="61" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="55" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="56" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="57" width="28.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="57" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="58" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="58" width="15.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="59" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="59" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="59" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="60" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="60" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="30">
@@ -1188,9 +1185,7 @@
       <c r="C15" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="51" t="s">
-        <v>48</v>
-      </c>
+      <c r="D15" s="21"/>
       <c r="E15" s="49" t="s">
         <v>46</v>
       </c>
@@ -1219,7 +1214,7 @@
         <v>25569.229166666668</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>45</v>
@@ -1252,7 +1247,7 @@
         <v>25569.229166666668</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D17" s="21" t="s">
         <v>45</v>
@@ -1285,7 +1280,7 @@
         <v>25569.229166666668</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D18" s="21" t="s">
         <v>45</v>
@@ -1318,7 +1313,7 @@
         <v>25569.229166666668</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D19" s="21" t="s">
         <v>30</v>
@@ -1326,7 +1321,9 @@
       <c r="E19" s="47">
         <v>46023.875</v>
       </c>
-      <c r="F19" s="48"/>
+      <c r="F19" s="48">
+        <v>46023.916666666664</v>
+      </c>
       <c r="G19" s="10">
         <f>IF(D19="P",1,0)</f>
       </c>
@@ -1348,10 +1345,18 @@
         <f>IF(A20="","",TEXT(A20,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="48"/>
+      <c r="C20" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="47">
+        <v>46023.791666666664</v>
+      </c>
+      <c r="F20" s="48">
+        <v>46023.833333333336</v>
+      </c>
       <c r="G20" s="10">
         <f>IF(D20="P",1,0)</f>
       </c>
@@ -4141,17 +4146,17 @@
       <c r="K132" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75" customFormat="1" s="40">
-      <c r="A133" s="52" t="s">
+      <c r="A133" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="B133" s="53"/>
+      <c r="B133" s="52"/>
       <c r="C133" s="32"/>
       <c r="D133" s="32"/>
-      <c r="E133" s="54"/>
-      <c r="F133" s="54"/>
-      <c r="G133" s="55"/>
-      <c r="H133" s="55"/>
-      <c r="I133" s="55"/>
+      <c r="E133" s="53"/>
+      <c r="F133" s="53"/>
+      <c r="G133" s="54"/>
+      <c r="H133" s="54"/>
+      <c r="I133" s="54"/>
       <c r="J133" s="32"/>
       <c r="K133" s="32"/>
     </row>

--- a/MERN_Stack_4_Month_Attendance_Sheet (2).xlsx
+++ b/MERN_Stack_4_Month_Attendance_Sheet (2).xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="55">
   <si>
     <t>MERN STACK COURSE — MONTH 4 ATTENDANCE</t>
   </si>
@@ -191,6 +191,9 @@
   </si>
   <si>
     <t>I have learned List and Links</t>
+  </si>
+  <si>
+    <t>I have lerned to build cv through  code using tagsand links</t>
   </si>
   <si>
     <t>How to use: Enter the course start date in the yellow cell, add the topic for each class, and select P, A, or L from the Attendance dropdown. The summary updates automatically.</t>
@@ -1378,8 +1381,12 @@
         <f>IF(A21="","",TEXT(A21,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="C21" s="36"/>
-      <c r="D21" s="21"/>
+      <c r="C21" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>36</v>
+      </c>
       <c r="E21" s="47"/>
       <c r="F21" s="48"/>
       <c r="G21" s="10">
@@ -1403,8 +1410,12 @@
         <f>IF(A22="","",TEXT(A22,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="21"/>
+      <c r="C22" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>36</v>
+      </c>
       <c r="E22" s="47"/>
       <c r="F22" s="48"/>
       <c r="G22" s="10">
@@ -1428,10 +1439,18 @@
         <f>IF(A23="","",TEXT(A23,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="48"/>
+      <c r="C23" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="47">
+        <v>46023.666666666664</v>
+      </c>
+      <c r="F23" s="48">
+        <v>46023.708333333336</v>
+      </c>
       <c r="G23" s="10">
         <f>IF(D23="P",1,0)</f>
       </c>
@@ -4147,7 +4166,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75" customFormat="1" s="40">
       <c r="A133" s="51" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B133" s="52"/>
       <c r="C133" s="32"/>

--- a/MERN_Stack_4_Month_Attendance_Sheet (2).xlsx
+++ b/MERN_Stack_4_Month_Attendance_Sheet (2).xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="57">
   <si>
     <t>MERN STACK COURSE — MONTH 4 ATTENDANCE</t>
   </si>
@@ -193,7 +193,13 @@
     <t>I have learned List and Links</t>
   </si>
   <si>
-    <t>I have lerned to build cv through  code using tagsand links</t>
+    <t>I have learned to build cv through  code using tagsand links</t>
+  </si>
+  <si>
+    <t>i have  learned images and link</t>
+  </si>
+  <si>
+    <t>I Have learned img,links,bonus ,multples programs</t>
   </si>
   <si>
     <t>How to use: Enter the course start date in the yellow cell, add the topic for each class, and select P, A, or L from the Attendance dropdown. The summary updates automatically.</t>
@@ -1306,7 +1312,7 @@
       <c r="J18" s="32"/>
       <c r="K18" s="32"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="8">
         <f>IF($B$8="","",$B$8+8)</f>
         <v>25569.229166666668</v>
@@ -1339,7 +1345,7 @@
       <c r="J19" s="32"/>
       <c r="K19" s="32"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="8">
         <f>IF($B$8="","",$B$8+9)</f>
         <v>25569.229166666668</v>
@@ -1372,7 +1378,7 @@
       <c r="J20" s="32"/>
       <c r="K20" s="32"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="8">
         <f>IF($B$8="","",$B$8+10)</f>
         <v>25569.229166666668</v>
@@ -1401,7 +1407,7 @@
       <c r="J21" s="32"/>
       <c r="K21" s="32"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="8">
         <f>IF($B$8="","",$B$8+11)</f>
         <v>25569.229166666668</v>
@@ -1430,7 +1436,7 @@
       <c r="J22" s="32"/>
       <c r="K22" s="32"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="8">
         <f>IF($B$8="","",$B$8+12)</f>
         <v>25569.229166666668</v>
@@ -1463,7 +1469,7 @@
       <c r="J23" s="32"/>
       <c r="K23" s="32"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="8">
         <f>IF($B$8="","",$B$8+13)</f>
         <v>25569.229166666668</v>
@@ -1472,10 +1478,18 @@
         <f>IF(A24="","",TEXT(A24,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="C24" s="36"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="48"/>
+      <c r="C24" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" s="47">
+        <v>46023.875</v>
+      </c>
+      <c r="F24" s="48">
+        <v>46023.916666666664</v>
+      </c>
       <c r="G24" s="10">
         <f>IF(D24="P",1,0)</f>
       </c>
@@ -1488,7 +1502,7 @@
       <c r="J24" s="32"/>
       <c r="K24" s="32"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="8">
         <f>IF($B$8="","",$B$8+14)</f>
         <v>25569.229166666668</v>
@@ -1497,9 +1511,15 @@
         <f>IF(A25="","",TEXT(A25,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="C25" s="36"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="47"/>
+      <c r="C25" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="47">
+        <v>46023.791666666664</v>
+      </c>
       <c r="F25" s="48"/>
       <c r="G25" s="10">
         <f>IF(D25="P",1,0)</f>
@@ -1513,7 +1533,7 @@
       <c r="J25" s="32"/>
       <c r="K25" s="32"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="8">
         <f>IF($B$8="","",$B$8+15)</f>
         <v>25569.229166666668</v>
@@ -4166,7 +4186,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75" customFormat="1" s="40">
       <c r="A133" s="51" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B133" s="52"/>
       <c r="C133" s="32"/>

--- a/MERN_Stack_4_Month_Attendance_Sheet (2).xlsx
+++ b/MERN_Stack_4_Month_Attendance_Sheet (2).xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="58">
   <si>
     <t>MERN STACK COURSE — MONTH 4 ATTENDANCE</t>
   </si>
@@ -200,6 +200,9 @@
   </si>
   <si>
     <t>I Have learned img,links,bonus ,multples programs</t>
+  </si>
+  <si>
+    <t>i have recall all tags,images,links,tables etc</t>
   </si>
   <si>
     <t>How to use: Enter the course start date in the yellow cell, add the topic for each class, and select P, A, or L from the Attendance dropdown. The summary updates automatically.</t>
@@ -1520,7 +1523,9 @@
       <c r="E25" s="47">
         <v>46023.791666666664</v>
       </c>
-      <c r="F25" s="48"/>
+      <c r="F25" s="48">
+        <v>46023.875</v>
+      </c>
       <c r="G25" s="10">
         <f>IF(D25="P",1,0)</f>
       </c>
@@ -1542,9 +1547,15 @@
         <f>IF(A26="","",TEXT(A26,"ddd"))</f>
         <v>25569.229166666668</v>
       </c>
-      <c r="C26" s="36"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="47"/>
+      <c r="C26" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="47">
+        <v>46023.875</v>
+      </c>
       <c r="F26" s="48"/>
       <c r="G26" s="10">
         <f>IF(D26="P",1,0)</f>
@@ -4186,7 +4197,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75" customFormat="1" s="40">
       <c r="A133" s="51" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B133" s="52"/>
       <c r="C133" s="32"/>

--- a/MERN_Stack_4_Month_Attendance_Sheet (2).xlsx
+++ b/MERN_Stack_4_Month_Attendance_Sheet (2).xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="25">
   <si>
     <t>MERN STACK COURSE — MONTH 4 ATTENDANCE</t>
   </si>
@@ -106,106 +106,7 @@
     <t>4-MONTH TOTAL</t>
   </si>
   <si>
-    <t>MERN STACK COURSE — 4 MONTH ATTENDANCE REGISTER</t>
-  </si>
-  <si>
-    <t>Course Name</t>
-  </si>
-  <si>
-    <t>MERN Stack Development</t>
-  </si>
-  <si>
-    <t>Attendance Codes</t>
-  </si>
-  <si>
-    <t>Duration</t>
-  </si>
-  <si>
-    <t>4 Months</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>Instructor</t>
-  </si>
-  <si>
-    <t>Ananya Hegde</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>Aysha Mehek</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>Batch / Mode</t>
-  </si>
-  <si>
-    <t>Online</t>
-  </si>
-  <si>
-    <t>Course Start Date</t>
-  </si>
-  <si>
-    <t>Start Time</t>
-  </si>
-  <si>
-    <t>End Time</t>
-  </si>
-  <si>
-    <t>Introduction to mern stack</t>
-  </si>
-  <si>
-    <t>Role of internet protocol</t>
-  </si>
-  <si>
-    <t>Structure of Html</t>
-  </si>
-  <si>
-    <t>p</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>_</t>
-  </si>
-  <si>
-    <t>Introduction to HTTP and HTTPS Uses and Applications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTML tags </t>
-  </si>
-  <si>
-    <t>Tables Tag</t>
-  </si>
-  <si>
-    <t>Text Formatting Examples</t>
-  </si>
-  <si>
-    <t>I have learned List and Links</t>
-  </si>
-  <si>
-    <t>I have learned to build cv through  code using tagsand links</t>
-  </si>
-  <si>
-    <t>i have  learned images and link</t>
-  </si>
-  <si>
-    <t>I Have learned img,links,bonus ,multples programs</t>
-  </si>
-  <si>
-    <t>i have recall all tags,images,links,tables etc</t>
-  </si>
-  <si>
-    <t>How to use: Enter the course start date in the yellow cell, add the topic for each class, and select P, A, or L from the Attendance dropdown. The summary updates automatically.</t>
+    <t/>
   </si>
 </sst>
 </file>
@@ -365,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="68">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -445,7 +346,7 @@
     <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="2" applyFill="1" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
@@ -466,43 +367,61 @@
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="5" applyFill="1" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="6" applyFill="1" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="168" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="168" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="167" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
@@ -511,13 +430,16 @@
     <xf xfId="0" numFmtId="167" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="168" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="168" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="168" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="168" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="7" applyFill="1" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
@@ -852,17 +774,17 @@
   <dimension ref="A1:K134"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="55" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="56" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="57" width="28.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="57" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="58" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="58" width="15.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="59" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="59" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="59" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="60" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="60" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="62" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="63" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="64" width="28.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="64" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="65" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="65" width="15.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="66" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="66" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="66" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="67" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="67" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="30">
@@ -895,17 +817,17 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="22">
       <c r="A3" s="34" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C3" s="36"/>
       <c r="D3" s="36"/>
       <c r="E3" s="30"/>
       <c r="F3" s="30"/>
       <c r="G3" s="37" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H3" s="31"/>
       <c r="I3" s="31"/>
@@ -914,20 +836,20 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="22">
       <c r="A4" s="34" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C4" s="36"/>
       <c r="D4" s="36"/>
       <c r="E4" s="30"/>
       <c r="F4" s="30"/>
       <c r="G4" s="38" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H4" s="38" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="I4" s="31"/>
       <c r="J4" s="32"/>
@@ -935,43 +857,43 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="22">
       <c r="A5" s="34" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C5" s="36"/>
       <c r="D5" s="36"/>
       <c r="E5" s="30"/>
       <c r="F5" s="30"/>
       <c r="G5" s="39" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="H5" s="39" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="I5" s="31"/>
       <c r="J5" s="32"/>
-      <c r="K5" s="32" t="s">
-        <v>34</v>
+      <c r="K5" s="40" t="s">
+        <v>24</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="22">
       <c r="A6" s="34" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C6" s="36"/>
       <c r="D6" s="36"/>
       <c r="E6" s="30"/>
       <c r="F6" s="30"/>
-      <c r="G6" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>17</v>
+      <c r="G6" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="41" t="s">
+        <v>24</v>
       </c>
       <c r="I6" s="31"/>
       <c r="J6" s="32"/>
@@ -979,10 +901,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="22">
       <c r="A7" s="34" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C7" s="36"/>
       <c r="D7" s="36"/>
@@ -996,11 +918,9 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="22">
       <c r="A8" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="35">
-        <v>46267</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B8" s="42"/>
       <c r="C8" s="36"/>
       <c r="D8" s="36"/>
       <c r="E8" s="30"/>
@@ -1024,3147 +944,2877 @@
       <c r="J9" s="32"/>
       <c r="K9" s="32"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75" customFormat="1" s="40">
-      <c r="A10" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="42" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="44" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="44" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="H10" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="I10" s="45" t="s">
-        <v>17</v>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75" customFormat="1" s="43">
+      <c r="A10" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="48" t="s">
+        <v>24</v>
       </c>
       <c r="J10" s="32"/>
       <c r="K10" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
-      <c r="A11" s="8">
-        <f>IF($B$8="","",$B$8+0)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B11" s="46">
-        <f>IF(A11="","",TEXT(A11,"ddd"))</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="47">
-        <v>46023.791666666664</v>
-      </c>
-      <c r="F11" s="48">
-        <v>46023.833333333336</v>
-      </c>
-      <c r="G11" s="10">
-        <f>IF(D11="P",1,0)</f>
-      </c>
-      <c r="H11" s="10">
-        <f>IF(D11="A",1,0)</f>
-      </c>
-      <c r="I11" s="10">
-        <f>IF(D11="L",1,0)</f>
+      <c r="A11" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="53"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J11" s="32"/>
       <c r="K11" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
-      <c r="A12" s="8">
-        <f>IF($B$8="","",$B$8+1)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B12" s="46">
-        <f>IF(A12="","",TEXT(A12,"ddd"))</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="C12" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="47">
-        <v>46023.833333333336</v>
-      </c>
-      <c r="F12" s="48"/>
-      <c r="G12" s="10">
-        <f>IF(D12="P",1,0)</f>
-      </c>
-      <c r="H12" s="10">
-        <f>IF(D12="A",1,0)</f>
-      </c>
-      <c r="I12" s="10">
-        <f>IF(D12="L",1,0)</f>
+      <c r="A12" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="53"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J12" s="32"/>
       <c r="K12" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
-      <c r="A13" s="8">
-        <f>IF($B$8="","",$B$8+2)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B13" s="46">
-        <f>IF(A13="","",TEXT(A13,"ddd"))</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="C13" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="47">
-        <v>46023.875</v>
-      </c>
-      <c r="F13" s="48">
-        <v>46023.916666666664</v>
-      </c>
-      <c r="G13" s="10">
-        <f>IF(D13="P",1,0)</f>
-      </c>
-      <c r="H13" s="10">
-        <f>IF(D13="A",1,0)</f>
-      </c>
-      <c r="I13" s="10">
-        <f>IF(D13="L",1,0)</f>
+      <c r="A13" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="53"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J13" s="32"/>
       <c r="K13" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
-      <c r="A14" s="8">
-        <f>IF($B$8="","",$B$8+3)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B14" s="46">
-        <f>IF(A14="","",TEXT(A14,"ddd"))</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="C14" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="49" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="50" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14" s="10">
-        <f>IF(D14="P",1,0)</f>
-      </c>
-      <c r="H14" s="10">
-        <f>IF(D14="A",1,0)</f>
-      </c>
-      <c r="I14" s="10">
-        <f>IF(D14="L",1,0)</f>
+      <c r="A14" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J14" s="32"/>
       <c r="K14" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
-      <c r="A15" s="8">
-        <f>IF($B$8="","",$B$8+4)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B15" s="46">
-        <f>IF(A15="","",TEXT(A15,"ddd"))</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="C15" s="36" t="s">
-        <v>47</v>
+      <c r="A15" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>24</v>
       </c>
       <c r="D15" s="21"/>
-      <c r="E15" s="49" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" s="50" t="s">
-        <v>46</v>
-      </c>
-      <c r="G15" s="10">
-        <f>IF(D15="P",1,0)</f>
-      </c>
-      <c r="H15" s="10">
-        <f>IF(D15="A",1,0)</f>
-      </c>
-      <c r="I15" s="10">
-        <f>IF(D15="L",1,0)</f>
+      <c r="E15" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J15" s="32"/>
       <c r="K15" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
-      <c r="A16" s="8">
-        <f>IF($B$8="","",$B$8+5)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B16" s="46">
-        <f>IF(A16="","",TEXT(A16,"ddd"))</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="C16" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="47">
-        <v>46023.791666666664</v>
-      </c>
-      <c r="F16" s="48">
-        <v>46023.833333333336</v>
-      </c>
-      <c r="G16" s="10">
-        <f>IF(D16="P",1,0)</f>
-      </c>
-      <c r="H16" s="10">
-        <f>IF(D16="A",1,0)</f>
-      </c>
-      <c r="I16" s="10">
-        <f>IF(D16="L",1,0)</f>
+      <c r="A16" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="53"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J16" s="32"/>
       <c r="K16" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
-      <c r="A17" s="8">
-        <f>IF($B$8="","",$B$8+6)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B17" s="46">
-        <f>IF(A17="","",TEXT(A17,"ddd"))</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="C17" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="47">
-        <v>46023.791666666664</v>
-      </c>
-      <c r="F17" s="48">
-        <v>46023.833333333336</v>
-      </c>
-      <c r="G17" s="10">
-        <f>IF(D17="P",1,0)</f>
-      </c>
-      <c r="H17" s="10">
-        <f>IF(D17="A",1,0)</f>
-      </c>
-      <c r="I17" s="10">
-        <f>IF(D17="L",1,0)</f>
+      <c r="A17" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="53"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H17" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J17" s="32"/>
       <c r="K17" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
-      <c r="A18" s="8">
-        <f>IF($B$8="","",$B$8+7)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B18" s="46">
-        <f>IF(A18="","",TEXT(A18,"ddd"))</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="C18" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" s="47">
-        <v>46023.875</v>
-      </c>
-      <c r="F18" s="48">
-        <v>46023.916666666664</v>
-      </c>
-      <c r="G18" s="10">
-        <f>IF(D18="P",1,0)</f>
-      </c>
-      <c r="H18" s="10">
-        <f>IF(D18="A",1,0)</f>
-      </c>
-      <c r="I18" s="10">
-        <f>IF(D18="L",1,0)</f>
+      <c r="A18" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="53"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J18" s="32"/>
       <c r="K18" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
-      <c r="A19" s="8">
-        <f>IF($B$8="","",$B$8+8)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B19" s="46">
-        <f>IF(A19="","",TEXT(A19,"ddd"))</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="C19" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="47">
-        <v>46023.875</v>
-      </c>
-      <c r="F19" s="48">
-        <v>46023.916666666664</v>
-      </c>
-      <c r="G19" s="10">
-        <f>IF(D19="P",1,0)</f>
-      </c>
-      <c r="H19" s="10">
-        <f>IF(D19="A",1,0)</f>
-      </c>
-      <c r="I19" s="10">
-        <f>IF(D19="L",1,0)</f>
+      <c r="A19" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="53"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H19" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J19" s="32"/>
       <c r="K19" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
-      <c r="A20" s="8">
-        <f>IF($B$8="","",$B$8+9)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B20" s="46">
-        <f>IF(A20="","",TEXT(A20,"ddd"))</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="C20" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" s="47">
-        <v>46023.791666666664</v>
-      </c>
-      <c r="F20" s="48">
-        <v>46023.833333333336</v>
-      </c>
-      <c r="G20" s="10">
-        <f>IF(D20="P",1,0)</f>
-      </c>
-      <c r="H20" s="10">
-        <f>IF(D20="A",1,0)</f>
-      </c>
-      <c r="I20" s="10">
-        <f>IF(D20="L",1,0)</f>
+      <c r="A20" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="53"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J20" s="32"/>
       <c r="K20" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
-      <c r="A21" s="8">
-        <f>IF($B$8="","",$B$8+10)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B21" s="46">
-        <f>IF(A21="","",TEXT(A21,"ddd"))</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="C21" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" s="47"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="10">
-        <f>IF(D21="P",1,0)</f>
-      </c>
-      <c r="H21" s="10">
-        <f>IF(D21="A",1,0)</f>
-      </c>
-      <c r="I21" s="10">
-        <f>IF(D21="L",1,0)</f>
+      <c r="A21" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="53"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J21" s="32"/>
       <c r="K21" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
-      <c r="A22" s="8">
-        <f>IF($B$8="","",$B$8+11)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B22" s="46">
-        <f>IF(A22="","",TEXT(A22,"ddd"))</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="C22" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" s="47"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="10">
-        <f>IF(D22="P",1,0)</f>
-      </c>
-      <c r="H22" s="10">
-        <f>IF(D22="A",1,0)</f>
-      </c>
-      <c r="I22" s="10">
-        <f>IF(D22="L",1,0)</f>
+      <c r="A22" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="53"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J22" s="32"/>
       <c r="K22" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
-      <c r="A23" s="8">
-        <f>IF($B$8="","",$B$8+12)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B23" s="46">
-        <f>IF(A23="","",TEXT(A23,"ddd"))</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="C23" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" s="47">
-        <v>46023.666666666664</v>
-      </c>
-      <c r="F23" s="48">
-        <v>46023.708333333336</v>
-      </c>
-      <c r="G23" s="10">
-        <f>IF(D23="P",1,0)</f>
-      </c>
-      <c r="H23" s="10">
-        <f>IF(D23="A",1,0)</f>
-      </c>
-      <c r="I23" s="10">
-        <f>IF(D23="L",1,0)</f>
+      <c r="A23" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="53"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J23" s="32"/>
       <c r="K23" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
-      <c r="A24" s="8">
-        <f>IF($B$8="","",$B$8+13)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B24" s="46">
-        <f>IF(A24="","",TEXT(A24,"ddd"))</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="C24" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="E24" s="47">
-        <v>46023.875</v>
-      </c>
-      <c r="F24" s="48">
-        <v>46023.916666666664</v>
-      </c>
-      <c r="G24" s="10">
-        <f>IF(D24="P",1,0)</f>
-      </c>
-      <c r="H24" s="10">
-        <f>IF(D24="A",1,0)</f>
-      </c>
-      <c r="I24" s="10">
-        <f>IF(D24="L",1,0)</f>
+      <c r="A24" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="53"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H24" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J24" s="32"/>
       <c r="K24" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
-      <c r="A25" s="8">
-        <f>IF($B$8="","",$B$8+14)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B25" s="46">
-        <f>IF(A25="","",TEXT(A25,"ddd"))</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="C25" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="E25" s="47">
-        <v>46023.791666666664</v>
-      </c>
-      <c r="F25" s="48">
-        <v>46023.875</v>
-      </c>
-      <c r="G25" s="10">
-        <f>IF(D25="P",1,0)</f>
-      </c>
-      <c r="H25" s="10">
-        <f>IF(D25="A",1,0)</f>
-      </c>
-      <c r="I25" s="10">
-        <f>IF(D25="L",1,0)</f>
+      <c r="A25" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="53"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H25" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I25" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J25" s="32"/>
       <c r="K25" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
-      <c r="A26" s="8">
-        <f>IF($B$8="","",$B$8+15)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B26" s="46">
-        <f>IF(A26="","",TEXT(A26,"ddd"))</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="C26" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="E26" s="47">
-        <v>46023.875</v>
-      </c>
-      <c r="F26" s="48"/>
-      <c r="G26" s="10">
-        <f>IF(D26="P",1,0)</f>
-      </c>
-      <c r="H26" s="10">
-        <f>IF(D26="A",1,0)</f>
-      </c>
-      <c r="I26" s="10">
-        <f>IF(D26="L",1,0)</f>
+      <c r="A26" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="53"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J26" s="32"/>
       <c r="K26" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
-      <c r="A27" s="8">
-        <f>IF($B$8="","",$B$8+16)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B27" s="46">
-        <f>IF(A27="","",TEXT(A27,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A27" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C27" s="36"/>
       <c r="D27" s="21"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="10">
-        <f>IF(D27="P",1,0)</f>
-      </c>
-      <c r="H27" s="10">
-        <f>IF(D27="A",1,0)</f>
-      </c>
-      <c r="I27" s="10">
-        <f>IF(D27="L",1,0)</f>
+      <c r="E27" s="53"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H27" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J27" s="32"/>
       <c r="K27" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
-      <c r="A28" s="8">
-        <f>IF($B$8="","",$B$8+17)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B28" s="46">
-        <f>IF(A28="","",TEXT(A28,"ddd"))</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="C28" s="36"/>
+      <c r="A28" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="51" t="s">
+        <v>24</v>
+      </c>
       <c r="D28" s="21"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="10">
-        <f>IF(D28="P",1,0)</f>
-      </c>
-      <c r="H28" s="10">
-        <f>IF(D28="A",1,0)</f>
-      </c>
-      <c r="I28" s="10">
-        <f>IF(D28="L",1,0)</f>
+      <c r="E28" s="53"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H28" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J28" s="32"/>
       <c r="K28" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
-      <c r="A29" s="8">
-        <f>IF($B$8="","",$B$8+18)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B29" s="46">
-        <f>IF(A29="","",TEXT(A29,"ddd"))</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="C29" s="36"/>
+      <c r="A29" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="51" t="s">
+        <v>24</v>
+      </c>
       <c r="D29" s="21"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="10">
-        <f>IF(D29="P",1,0)</f>
-      </c>
-      <c r="H29" s="10">
-        <f>IF(D29="A",1,0)</f>
-      </c>
-      <c r="I29" s="10">
-        <f>IF(D29="L",1,0)</f>
+      <c r="E29" s="53"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H29" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J29" s="32"/>
       <c r="K29" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
-      <c r="A30" s="8">
-        <f>IF($B$8="","",$B$8+19)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B30" s="46">
-        <f>IF(A30="","",TEXT(A30,"ddd"))</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="C30" s="36"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="47"/>
-      <c r="F30" s="48"/>
-      <c r="G30" s="10">
-        <f>IF(D30="P",1,0)</f>
-      </c>
-      <c r="H30" s="10">
-        <f>IF(D30="A",1,0)</f>
-      </c>
-      <c r="I30" s="10">
-        <f>IF(D30="L",1,0)</f>
+      <c r="A30" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="53"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H30" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J30" s="32"/>
       <c r="K30" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
-      <c r="A31" s="8">
-        <f>IF($B$8="","",$B$8+20)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B31" s="46">
-        <f>IF(A31="","",TEXT(A31,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A31" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C31" s="36"/>
       <c r="D31" s="21"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="10">
-        <f>IF(D31="P",1,0)</f>
-      </c>
-      <c r="H31" s="10">
-        <f>IF(D31="A",1,0)</f>
-      </c>
-      <c r="I31" s="10">
-        <f>IF(D31="L",1,0)</f>
+      <c r="E31" s="53"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H31" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J31" s="32"/>
       <c r="K31" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
-      <c r="A32" s="8">
-        <f>IF($B$8="","",$B$8+21)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B32" s="46">
-        <f>IF(A32="","",TEXT(A32,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A32" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C32" s="36"/>
       <c r="D32" s="21"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="10">
-        <f>IF(D32="P",1,0)</f>
-      </c>
-      <c r="H32" s="10">
-        <f>IF(D32="A",1,0)</f>
-      </c>
-      <c r="I32" s="10">
-        <f>IF(D32="L",1,0)</f>
+      <c r="E32" s="53"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H32" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J32" s="32"/>
       <c r="K32" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
-      <c r="A33" s="8">
-        <f>IF($B$8="","",$B$8+22)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B33" s="46">
-        <f>IF(A33="","",TEXT(A33,"ddd"))</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="C33" s="36"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="10">
-        <f>IF(D33="P",1,0)</f>
-      </c>
-      <c r="H33" s="10">
-        <f>IF(D33="A",1,0)</f>
-      </c>
-      <c r="I33" s="10">
-        <f>IF(D33="L",1,0)</f>
+      <c r="A33" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" s="52" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="53"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H33" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I33" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J33" s="32"/>
       <c r="K33" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
-      <c r="A34" s="8">
-        <f>IF($B$8="","",$B$8+23)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B34" s="46">
-        <f>IF(A34="","",TEXT(A34,"ddd"))</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="C34" s="36"/>
+      <c r="A34" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>24</v>
+      </c>
       <c r="D34" s="21"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="10">
-        <f>IF(D34="P",1,0)</f>
-      </c>
-      <c r="H34" s="10">
-        <f>IF(D34="A",1,0)</f>
-      </c>
-      <c r="I34" s="10">
-        <f>IF(D34="L",1,0)</f>
+      <c r="E34" s="53"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H34" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I34" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J34" s="32"/>
       <c r="K34" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
-      <c r="A35" s="8">
-        <f>IF($B$8="","",$B$8+24)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B35" s="46">
-        <f>IF(A35="","",TEXT(A35,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A35" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C35" s="36"/>
       <c r="D35" s="21"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="10">
-        <f>IF(D35="P",1,0)</f>
-      </c>
-      <c r="H35" s="10">
-        <f>IF(D35="A",1,0)</f>
-      </c>
-      <c r="I35" s="10">
-        <f>IF(D35="L",1,0)</f>
+      <c r="E35" s="53"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J35" s="32"/>
       <c r="K35" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
-      <c r="A36" s="8">
-        <f>IF($B$8="","",$B$8+25)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B36" s="46">
-        <f>IF(A36="","",TEXT(A36,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A36" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C36" s="36"/>
       <c r="D36" s="21"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="10">
-        <f>IF(D36="P",1,0)</f>
-      </c>
-      <c r="H36" s="10">
-        <f>IF(D36="A",1,0)</f>
-      </c>
-      <c r="I36" s="10">
-        <f>IF(D36="L",1,0)</f>
+      <c r="E36" s="53"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H36" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J36" s="32"/>
       <c r="K36" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
-      <c r="A37" s="8">
-        <f>IF($B$8="","",$B$8+26)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B37" s="46">
-        <f>IF(A37="","",TEXT(A37,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A37" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B37" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C37" s="36"/>
       <c r="D37" s="21"/>
-      <c r="E37" s="47"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="10">
-        <f>IF(D37="P",1,0)</f>
-      </c>
-      <c r="H37" s="10">
-        <f>IF(D37="A",1,0)</f>
-      </c>
-      <c r="I37" s="10">
-        <f>IF(D37="L",1,0)</f>
+      <c r="E37" s="53"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H37" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I37" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J37" s="32"/>
       <c r="K37" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
-      <c r="A38" s="8">
-        <f>IF($B$8="","",$B$8+27)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B38" s="46">
-        <f>IF(A38="","",TEXT(A38,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A38" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B38" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C38" s="36"/>
       <c r="D38" s="21"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="48"/>
-      <c r="G38" s="10">
-        <f>IF(D38="P",1,0)</f>
-      </c>
-      <c r="H38" s="10">
-        <f>IF(D38="A",1,0)</f>
-      </c>
-      <c r="I38" s="10">
-        <f>IF(D38="L",1,0)</f>
+      <c r="E38" s="53"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H38" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I38" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J38" s="32"/>
       <c r="K38" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
-      <c r="A39" s="8">
-        <f>IF($B$8="","",$B$8+28)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B39" s="46">
-        <f>IF(A39="","",TEXT(A39,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A39" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C39" s="36"/>
       <c r="D39" s="21"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="48"/>
-      <c r="G39" s="10">
-        <f>IF(D39="P",1,0)</f>
-      </c>
-      <c r="H39" s="10">
-        <f>IF(D39="A",1,0)</f>
-      </c>
-      <c r="I39" s="10">
-        <f>IF(D39="L",1,0)</f>
+      <c r="E39" s="53"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H39" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I39" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J39" s="32"/>
       <c r="K39" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
-      <c r="A40" s="8">
-        <f>IF($B$8="","",$B$8+29)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B40" s="46">
-        <f>IF(A40="","",TEXT(A40,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A40" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C40" s="36"/>
       <c r="D40" s="21"/>
-      <c r="E40" s="47"/>
-      <c r="F40" s="48"/>
-      <c r="G40" s="10">
-        <f>IF(D40="P",1,0)</f>
-      </c>
-      <c r="H40" s="10">
-        <f>IF(D40="A",1,0)</f>
-      </c>
-      <c r="I40" s="10">
-        <f>IF(D40="L",1,0)</f>
+      <c r="E40" s="53"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H40" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I40" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J40" s="32"/>
       <c r="K40" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
-      <c r="A41" s="8">
-        <f>IF($B$8="","",$B$8+30)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B41" s="46">
-        <f>IF(A41="","",TEXT(A41,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A41" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B41" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C41" s="36"/>
       <c r="D41" s="21"/>
-      <c r="E41" s="47"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="10">
-        <f>IF(D41="P",1,0)</f>
-      </c>
-      <c r="H41" s="10">
-        <f>IF(D41="A",1,0)</f>
-      </c>
-      <c r="I41" s="10">
-        <f>IF(D41="L",1,0)</f>
+      <c r="E41" s="53"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H41" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I41" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J41" s="32"/>
       <c r="K41" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
-      <c r="A42" s="8">
-        <f>IF($B$8="","",$B$8+31)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B42" s="46">
-        <f>IF(A42="","",TEXT(A42,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A42" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B42" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C42" s="36"/>
       <c r="D42" s="21"/>
-      <c r="E42" s="47"/>
-      <c r="F42" s="48"/>
-      <c r="G42" s="10">
-        <f>IF(D42="P",1,0)</f>
-      </c>
-      <c r="H42" s="10">
-        <f>IF(D42="A",1,0)</f>
-      </c>
-      <c r="I42" s="10">
-        <f>IF(D42="L",1,0)</f>
+      <c r="E42" s="53"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H42" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J42" s="32"/>
       <c r="K42" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
-      <c r="A43" s="8">
-        <f>IF($B$8="","",$B$8+32)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B43" s="46">
-        <f>IF(A43="","",TEXT(A43,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A43" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B43" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C43" s="36"/>
       <c r="D43" s="21"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="48"/>
-      <c r="G43" s="10">
-        <f>IF(D43="P",1,0)</f>
-      </c>
-      <c r="H43" s="10">
-        <f>IF(D43="A",1,0)</f>
-      </c>
-      <c r="I43" s="10">
-        <f>IF(D43="L",1,0)</f>
+      <c r="E43" s="53"/>
+      <c r="F43" s="54"/>
+      <c r="G43" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H43" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I43" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J43" s="32"/>
       <c r="K43" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
-      <c r="A44" s="8">
-        <f>IF($B$8="","",$B$8+33)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B44" s="46">
-        <f>IF(A44="","",TEXT(A44,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A44" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C44" s="36"/>
       <c r="D44" s="21"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="48"/>
-      <c r="G44" s="10">
-        <f>IF(D44="P",1,0)</f>
-      </c>
-      <c r="H44" s="10">
-        <f>IF(D44="A",1,0)</f>
-      </c>
-      <c r="I44" s="10">
-        <f>IF(D44="L",1,0)</f>
+      <c r="E44" s="53"/>
+      <c r="F44" s="54"/>
+      <c r="G44" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H44" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I44" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J44" s="32"/>
       <c r="K44" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
-      <c r="A45" s="8">
-        <f>IF($B$8="","",$B$8+34)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B45" s="46">
-        <f>IF(A45="","",TEXT(A45,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A45" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B45" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C45" s="36"/>
       <c r="D45" s="21"/>
-      <c r="E45" s="47"/>
-      <c r="F45" s="48"/>
-      <c r="G45" s="10">
-        <f>IF(D45="P",1,0)</f>
-      </c>
-      <c r="H45" s="10">
-        <f>IF(D45="A",1,0)</f>
-      </c>
-      <c r="I45" s="10">
-        <f>IF(D45="L",1,0)</f>
+      <c r="E45" s="53"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H45" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I45" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J45" s="32"/>
       <c r="K45" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
-      <c r="A46" s="8">
-        <f>IF($B$8="","",$B$8+35)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B46" s="46">
-        <f>IF(A46="","",TEXT(A46,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A46" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B46" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C46" s="36"/>
       <c r="D46" s="21"/>
-      <c r="E46" s="47"/>
-      <c r="F46" s="48"/>
-      <c r="G46" s="10">
-        <f>IF(D46="P",1,0)</f>
-      </c>
-      <c r="H46" s="10">
-        <f>IF(D46="A",1,0)</f>
-      </c>
-      <c r="I46" s="10">
-        <f>IF(D46="L",1,0)</f>
+      <c r="E46" s="53"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H46" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I46" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J46" s="32"/>
       <c r="K46" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
-      <c r="A47" s="8">
-        <f>IF($B$8="","",$B$8+36)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B47" s="46">
-        <f>IF(A47="","",TEXT(A47,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A47" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B47" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C47" s="36"/>
       <c r="D47" s="21"/>
-      <c r="E47" s="47"/>
-      <c r="F47" s="48"/>
-      <c r="G47" s="10">
-        <f>IF(D47="P",1,0)</f>
-      </c>
-      <c r="H47" s="10">
-        <f>IF(D47="A",1,0)</f>
-      </c>
-      <c r="I47" s="10">
-        <f>IF(D47="L",1,0)</f>
+      <c r="E47" s="53"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H47" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J47" s="32"/>
       <c r="K47" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
-      <c r="A48" s="8">
-        <f>IF($B$8="","",$B$8+37)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B48" s="46">
-        <f>IF(A48="","",TEXT(A48,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A48" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C48" s="36"/>
       <c r="D48" s="21"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="48"/>
-      <c r="G48" s="10">
-        <f>IF(D48="P",1,0)</f>
-      </c>
-      <c r="H48" s="10">
-        <f>IF(D48="A",1,0)</f>
-      </c>
-      <c r="I48" s="10">
-        <f>IF(D48="L",1,0)</f>
+      <c r="E48" s="53"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H48" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I48" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J48" s="32"/>
       <c r="K48" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
-      <c r="A49" s="8">
-        <f>IF($B$8="","",$B$8+38)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B49" s="46">
-        <f>IF(A49="","",TEXT(A49,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A49" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B49" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C49" s="36"/>
       <c r="D49" s="21"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="10">
-        <f>IF(D49="P",1,0)</f>
-      </c>
-      <c r="H49" s="10">
-        <f>IF(D49="A",1,0)</f>
-      </c>
-      <c r="I49" s="10">
-        <f>IF(D49="L",1,0)</f>
+      <c r="E49" s="53"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H49" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I49" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J49" s="32"/>
       <c r="K49" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
-      <c r="A50" s="8">
-        <f>IF($B$8="","",$B$8+39)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B50" s="46">
-        <f>IF(A50="","",TEXT(A50,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A50" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B50" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C50" s="36"/>
       <c r="D50" s="21"/>
-      <c r="E50" s="47"/>
-      <c r="F50" s="48"/>
-      <c r="G50" s="10">
-        <f>IF(D50="P",1,0)</f>
-      </c>
-      <c r="H50" s="10">
-        <f>IF(D50="A",1,0)</f>
-      </c>
-      <c r="I50" s="10">
-        <f>IF(D50="L",1,0)</f>
+      <c r="E50" s="53"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H50" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I50" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J50" s="32"/>
       <c r="K50" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
-      <c r="A51" s="8">
-        <f>IF($B$8="","",$B$8+40)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B51" s="46">
-        <f>IF(A51="","",TEXT(A51,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A51" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B51" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C51" s="36"/>
       <c r="D51" s="21"/>
-      <c r="E51" s="47"/>
-      <c r="F51" s="48"/>
-      <c r="G51" s="10">
-        <f>IF(D51="P",1,0)</f>
-      </c>
-      <c r="H51" s="10">
-        <f>IF(D51="A",1,0)</f>
-      </c>
-      <c r="I51" s="10">
-        <f>IF(D51="L",1,0)</f>
+      <c r="E51" s="53"/>
+      <c r="F51" s="54"/>
+      <c r="G51" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H51" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I51" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J51" s="32"/>
       <c r="K51" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
-      <c r="A52" s="8">
-        <f>IF($B$8="","",$B$8+41)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B52" s="46">
-        <f>IF(A52="","",TEXT(A52,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A52" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C52" s="36"/>
       <c r="D52" s="21"/>
-      <c r="E52" s="47"/>
-      <c r="F52" s="48"/>
-      <c r="G52" s="10">
-        <f>IF(D52="P",1,0)</f>
-      </c>
-      <c r="H52" s="10">
-        <f>IF(D52="A",1,0)</f>
-      </c>
-      <c r="I52" s="10">
-        <f>IF(D52="L",1,0)</f>
+      <c r="E52" s="53"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H52" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I52" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J52" s="32"/>
       <c r="K52" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
-      <c r="A53" s="8">
-        <f>IF($B$8="","",$B$8+42)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B53" s="46">
-        <f>IF(A53="","",TEXT(A53,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A53" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B53" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C53" s="36"/>
       <c r="D53" s="21"/>
-      <c r="E53" s="47"/>
-      <c r="F53" s="48"/>
-      <c r="G53" s="10">
-        <f>IF(D53="P",1,0)</f>
-      </c>
-      <c r="H53" s="10">
-        <f>IF(D53="A",1,0)</f>
-      </c>
-      <c r="I53" s="10">
-        <f>IF(D53="L",1,0)</f>
+      <c r="E53" s="53"/>
+      <c r="F53" s="54"/>
+      <c r="G53" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H53" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I53" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J53" s="32"/>
       <c r="K53" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
-      <c r="A54" s="8">
-        <f>IF($B$8="","",$B$8+43)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B54" s="46">
-        <f>IF(A54="","",TEXT(A54,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A54" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B54" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C54" s="36"/>
       <c r="D54" s="21"/>
-      <c r="E54" s="47"/>
-      <c r="F54" s="48"/>
-      <c r="G54" s="10">
-        <f>IF(D54="P",1,0)</f>
-      </c>
-      <c r="H54" s="10">
-        <f>IF(D54="A",1,0)</f>
-      </c>
-      <c r="I54" s="10">
-        <f>IF(D54="L",1,0)</f>
+      <c r="E54" s="53"/>
+      <c r="F54" s="54"/>
+      <c r="G54" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H54" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I54" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J54" s="32"/>
       <c r="K54" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
-      <c r="A55" s="8">
-        <f>IF($B$8="","",$B$8+44)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B55" s="46">
-        <f>IF(A55="","",TEXT(A55,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A55" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B55" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C55" s="36"/>
       <c r="D55" s="21"/>
-      <c r="E55" s="47"/>
-      <c r="F55" s="48"/>
-      <c r="G55" s="10">
-        <f>IF(D55="P",1,0)</f>
-      </c>
-      <c r="H55" s="10">
-        <f>IF(D55="A",1,0)</f>
-      </c>
-      <c r="I55" s="10">
-        <f>IF(D55="L",1,0)</f>
+      <c r="E55" s="53"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H55" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I55" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J55" s="32"/>
       <c r="K55" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
-      <c r="A56" s="8">
-        <f>IF($B$8="","",$B$8+45)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B56" s="46">
-        <f>IF(A56="","",TEXT(A56,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A56" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B56" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C56" s="36"/>
       <c r="D56" s="21"/>
-      <c r="E56" s="47"/>
-      <c r="F56" s="48"/>
-      <c r="G56" s="10">
-        <f>IF(D56="P",1,0)</f>
-      </c>
-      <c r="H56" s="10">
-        <f>IF(D56="A",1,0)</f>
-      </c>
-      <c r="I56" s="10">
-        <f>IF(D56="L",1,0)</f>
+      <c r="E56" s="53"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H56" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I56" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J56" s="32"/>
       <c r="K56" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
-      <c r="A57" s="8">
-        <f>IF($B$8="","",$B$8+46)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B57" s="46">
-        <f>IF(A57="","",TEXT(A57,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A57" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B57" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C57" s="36"/>
       <c r="D57" s="21"/>
-      <c r="E57" s="47"/>
-      <c r="F57" s="48"/>
-      <c r="G57" s="10">
-        <f>IF(D57="P",1,0)</f>
-      </c>
-      <c r="H57" s="10">
-        <f>IF(D57="A",1,0)</f>
-      </c>
-      <c r="I57" s="10">
-        <f>IF(D57="L",1,0)</f>
+      <c r="E57" s="53"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H57" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I57" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J57" s="32"/>
       <c r="K57" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
-      <c r="A58" s="8">
-        <f>IF($B$8="","",$B$8+47)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B58" s="46">
-        <f>IF(A58="","",TEXT(A58,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A58" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B58" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C58" s="36"/>
       <c r="D58" s="21"/>
-      <c r="E58" s="47"/>
-      <c r="F58" s="48"/>
-      <c r="G58" s="10">
-        <f>IF(D58="P",1,0)</f>
-      </c>
-      <c r="H58" s="10">
-        <f>IF(D58="A",1,0)</f>
-      </c>
-      <c r="I58" s="10">
-        <f>IF(D58="L",1,0)</f>
+      <c r="E58" s="53"/>
+      <c r="F58" s="54"/>
+      <c r="G58" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H58" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I58" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J58" s="32"/>
       <c r="K58" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
-      <c r="A59" s="8">
-        <f>IF($B$8="","",$B$8+48)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B59" s="46">
-        <f>IF(A59="","",TEXT(A59,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A59" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B59" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C59" s="36"/>
       <c r="D59" s="21"/>
-      <c r="E59" s="47"/>
-      <c r="F59" s="48"/>
-      <c r="G59" s="10">
-        <f>IF(D59="P",1,0)</f>
-      </c>
-      <c r="H59" s="10">
-        <f>IF(D59="A",1,0)</f>
-      </c>
-      <c r="I59" s="10">
-        <f>IF(D59="L",1,0)</f>
+      <c r="E59" s="53"/>
+      <c r="F59" s="54"/>
+      <c r="G59" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H59" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I59" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J59" s="32"/>
       <c r="K59" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
-      <c r="A60" s="8">
-        <f>IF($B$8="","",$B$8+49)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B60" s="46">
-        <f>IF(A60="","",TEXT(A60,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A60" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B60" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C60" s="36"/>
       <c r="D60" s="21"/>
-      <c r="E60" s="47"/>
-      <c r="F60" s="48"/>
-      <c r="G60" s="10">
-        <f>IF(D60="P",1,0)</f>
-      </c>
-      <c r="H60" s="10">
-        <f>IF(D60="A",1,0)</f>
-      </c>
-      <c r="I60" s="10">
-        <f>IF(D60="L",1,0)</f>
+      <c r="E60" s="53"/>
+      <c r="F60" s="54"/>
+      <c r="G60" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H60" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I60" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J60" s="32"/>
       <c r="K60" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
-      <c r="A61" s="8">
-        <f>IF($B$8="","",$B$8+50)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B61" s="46">
-        <f>IF(A61="","",TEXT(A61,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A61" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B61" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C61" s="36"/>
       <c r="D61" s="21"/>
-      <c r="E61" s="47"/>
-      <c r="F61" s="48"/>
-      <c r="G61" s="10">
-        <f>IF(D61="P",1,0)</f>
-      </c>
-      <c r="H61" s="10">
-        <f>IF(D61="A",1,0)</f>
-      </c>
-      <c r="I61" s="10">
-        <f>IF(D61="L",1,0)</f>
+      <c r="E61" s="53"/>
+      <c r="F61" s="54"/>
+      <c r="G61" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H61" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I61" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J61" s="32"/>
       <c r="K61" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
-      <c r="A62" s="8">
-        <f>IF($B$8="","",$B$8+51)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B62" s="46">
-        <f>IF(A62="","",TEXT(A62,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A62" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B62" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C62" s="36"/>
       <c r="D62" s="21"/>
-      <c r="E62" s="47"/>
-      <c r="F62" s="48"/>
-      <c r="G62" s="10">
-        <f>IF(D62="P",1,0)</f>
-      </c>
-      <c r="H62" s="10">
-        <f>IF(D62="A",1,0)</f>
-      </c>
-      <c r="I62" s="10">
-        <f>IF(D62="L",1,0)</f>
+      <c r="E62" s="53"/>
+      <c r="F62" s="54"/>
+      <c r="G62" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H62" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I62" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J62" s="32"/>
       <c r="K62" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
-      <c r="A63" s="8">
-        <f>IF($B$8="","",$B$8+52)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B63" s="46">
-        <f>IF(A63="","",TEXT(A63,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A63" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B63" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C63" s="36"/>
       <c r="D63" s="21"/>
-      <c r="E63" s="47"/>
-      <c r="F63" s="48"/>
-      <c r="G63" s="10">
-        <f>IF(D63="P",1,0)</f>
-      </c>
-      <c r="H63" s="10">
-        <f>IF(D63="A",1,0)</f>
-      </c>
-      <c r="I63" s="10">
-        <f>IF(D63="L",1,0)</f>
+      <c r="E63" s="53"/>
+      <c r="F63" s="54"/>
+      <c r="G63" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H63" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I63" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J63" s="32"/>
       <c r="K63" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
-      <c r="A64" s="8">
-        <f>IF($B$8="","",$B$8+53)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B64" s="46">
-        <f>IF(A64="","",TEXT(A64,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A64" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B64" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C64" s="36"/>
       <c r="D64" s="21"/>
-      <c r="E64" s="47"/>
-      <c r="F64" s="48"/>
-      <c r="G64" s="10">
-        <f>IF(D64="P",1,0)</f>
-      </c>
-      <c r="H64" s="10">
-        <f>IF(D64="A",1,0)</f>
-      </c>
-      <c r="I64" s="10">
-        <f>IF(D64="L",1,0)</f>
+      <c r="E64" s="53"/>
+      <c r="F64" s="54"/>
+      <c r="G64" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H64" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I64" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J64" s="32"/>
       <c r="K64" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
-      <c r="A65" s="8">
-        <f>IF($B$8="","",$B$8+54)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B65" s="46">
-        <f>IF(A65="","",TEXT(A65,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A65" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B65" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C65" s="36"/>
       <c r="D65" s="21"/>
-      <c r="E65" s="47"/>
-      <c r="F65" s="48"/>
-      <c r="G65" s="10">
-        <f>IF(D65="P",1,0)</f>
-      </c>
-      <c r="H65" s="10">
-        <f>IF(D65="A",1,0)</f>
-      </c>
-      <c r="I65" s="10">
-        <f>IF(D65="L",1,0)</f>
+      <c r="E65" s="53"/>
+      <c r="F65" s="54"/>
+      <c r="G65" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H65" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I65" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J65" s="32"/>
       <c r="K65" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
-      <c r="A66" s="8">
-        <f>IF($B$8="","",$B$8+55)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B66" s="46">
-        <f>IF(A66="","",TEXT(A66,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A66" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B66" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C66" s="36"/>
       <c r="D66" s="21"/>
-      <c r="E66" s="47"/>
-      <c r="F66" s="48"/>
-      <c r="G66" s="10">
-        <f>IF(D66="P",1,0)</f>
-      </c>
-      <c r="H66" s="10">
-        <f>IF(D66="A",1,0)</f>
-      </c>
-      <c r="I66" s="10">
-        <f>IF(D66="L",1,0)</f>
+      <c r="E66" s="53"/>
+      <c r="F66" s="54"/>
+      <c r="G66" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H66" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I66" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J66" s="32"/>
       <c r="K66" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
-      <c r="A67" s="8">
-        <f>IF($B$8="","",$B$8+56)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B67" s="46">
-        <f>IF(A67="","",TEXT(A67,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A67" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B67" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C67" s="36"/>
       <c r="D67" s="21"/>
-      <c r="E67" s="47"/>
-      <c r="F67" s="48"/>
-      <c r="G67" s="10">
-        <f>IF(D67="P",1,0)</f>
-      </c>
-      <c r="H67" s="10">
-        <f>IF(D67="A",1,0)</f>
-      </c>
-      <c r="I67" s="10">
-        <f>IF(D67="L",1,0)</f>
+      <c r="E67" s="53"/>
+      <c r="F67" s="54"/>
+      <c r="G67" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H67" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I67" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J67" s="32"/>
       <c r="K67" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
-      <c r="A68" s="8">
-        <f>IF($B$8="","",$B$8+57)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B68" s="46">
-        <f>IF(A68="","",TEXT(A68,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A68" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B68" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C68" s="36"/>
       <c r="D68" s="21"/>
-      <c r="E68" s="47"/>
-      <c r="F68" s="48"/>
-      <c r="G68" s="10">
-        <f>IF(D68="P",1,0)</f>
-      </c>
-      <c r="H68" s="10">
-        <f>IF(D68="A",1,0)</f>
-      </c>
-      <c r="I68" s="10">
-        <f>IF(D68="L",1,0)</f>
+      <c r="E68" s="53"/>
+      <c r="F68" s="54"/>
+      <c r="G68" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H68" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I68" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J68" s="32"/>
       <c r="K68" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
-      <c r="A69" s="8">
-        <f>IF($B$8="","",$B$8+58)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B69" s="46">
-        <f>IF(A69="","",TEXT(A69,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A69" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B69" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C69" s="36"/>
       <c r="D69" s="21"/>
-      <c r="E69" s="47"/>
-      <c r="F69" s="48"/>
-      <c r="G69" s="10">
-        <f>IF(D69="P",1,0)</f>
-      </c>
-      <c r="H69" s="10">
-        <f>IF(D69="A",1,0)</f>
-      </c>
-      <c r="I69" s="10">
-        <f>IF(D69="L",1,0)</f>
+      <c r="E69" s="53"/>
+      <c r="F69" s="54"/>
+      <c r="G69" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H69" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I69" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J69" s="32"/>
       <c r="K69" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
-      <c r="A70" s="8">
-        <f>IF($B$8="","",$B$8+59)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B70" s="46">
-        <f>IF(A70="","",TEXT(A70,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A70" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B70" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C70" s="36"/>
       <c r="D70" s="21"/>
-      <c r="E70" s="47"/>
-      <c r="F70" s="48"/>
-      <c r="G70" s="10">
-        <f>IF(D70="P",1,0)</f>
-      </c>
-      <c r="H70" s="10">
-        <f>IF(D70="A",1,0)</f>
-      </c>
-      <c r="I70" s="10">
-        <f>IF(D70="L",1,0)</f>
+      <c r="E70" s="53"/>
+      <c r="F70" s="54"/>
+      <c r="G70" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H70" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I70" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J70" s="32"/>
       <c r="K70" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
-      <c r="A71" s="8">
-        <f>IF($B$8="","",$B$8+60)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B71" s="46">
-        <f>IF(A71="","",TEXT(A71,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A71" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B71" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C71" s="36"/>
       <c r="D71" s="21"/>
-      <c r="E71" s="47"/>
-      <c r="F71" s="48"/>
-      <c r="G71" s="10">
-        <f>IF(D71="P",1,0)</f>
-      </c>
-      <c r="H71" s="10">
-        <f>IF(D71="A",1,0)</f>
-      </c>
-      <c r="I71" s="10">
-        <f>IF(D71="L",1,0)</f>
+      <c r="E71" s="53"/>
+      <c r="F71" s="54"/>
+      <c r="G71" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H71" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I71" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J71" s="32"/>
       <c r="K71" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
-      <c r="A72" s="8">
-        <f>IF($B$8="","",$B$8+61)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B72" s="46">
-        <f>IF(A72="","",TEXT(A72,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A72" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B72" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C72" s="36"/>
       <c r="D72" s="21"/>
-      <c r="E72" s="47"/>
-      <c r="F72" s="48"/>
-      <c r="G72" s="10">
-        <f>IF(D72="P",1,0)</f>
-      </c>
-      <c r="H72" s="10">
-        <f>IF(D72="A",1,0)</f>
-      </c>
-      <c r="I72" s="10">
-        <f>IF(D72="L",1,0)</f>
+      <c r="E72" s="53"/>
+      <c r="F72" s="54"/>
+      <c r="G72" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H72" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I72" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J72" s="32"/>
       <c r="K72" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
-      <c r="A73" s="8">
-        <f>IF($B$8="","",$B$8+62)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B73" s="46">
-        <f>IF(A73="","",TEXT(A73,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A73" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B73" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C73" s="36"/>
       <c r="D73" s="21"/>
-      <c r="E73" s="47"/>
-      <c r="F73" s="48"/>
-      <c r="G73" s="10">
-        <f>IF(D73="P",1,0)</f>
-      </c>
-      <c r="H73" s="10">
-        <f>IF(D73="A",1,0)</f>
-      </c>
-      <c r="I73" s="10">
-        <f>IF(D73="L",1,0)</f>
+      <c r="E73" s="53"/>
+      <c r="F73" s="54"/>
+      <c r="G73" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H73" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I73" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J73" s="32"/>
       <c r="K73" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
-      <c r="A74" s="8">
-        <f>IF($B$8="","",$B$8+63)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B74" s="46">
-        <f>IF(A74="","",TEXT(A74,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A74" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B74" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C74" s="36"/>
       <c r="D74" s="21"/>
-      <c r="E74" s="47"/>
-      <c r="F74" s="48"/>
-      <c r="G74" s="10">
-        <f>IF(D74="P",1,0)</f>
-      </c>
-      <c r="H74" s="10">
-        <f>IF(D74="A",1,0)</f>
-      </c>
-      <c r="I74" s="10">
-        <f>IF(D74="L",1,0)</f>
+      <c r="E74" s="53"/>
+      <c r="F74" s="54"/>
+      <c r="G74" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H74" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I74" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J74" s="32"/>
       <c r="K74" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
-      <c r="A75" s="8">
-        <f>IF($B$8="","",$B$8+64)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B75" s="46">
-        <f>IF(A75="","",TEXT(A75,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A75" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B75" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C75" s="36"/>
       <c r="D75" s="21"/>
-      <c r="E75" s="47"/>
-      <c r="F75" s="48"/>
-      <c r="G75" s="10">
-        <f>IF(D75="P",1,0)</f>
-      </c>
-      <c r="H75" s="10">
-        <f>IF(D75="A",1,0)</f>
-      </c>
-      <c r="I75" s="10">
-        <f>IF(D75="L",1,0)</f>
+      <c r="E75" s="53"/>
+      <c r="F75" s="54"/>
+      <c r="G75" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H75" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I75" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J75" s="32"/>
       <c r="K75" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
-      <c r="A76" s="8">
-        <f>IF($B$8="","",$B$8+65)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B76" s="46">
-        <f>IF(A76="","",TEXT(A76,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A76" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B76" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C76" s="36"/>
       <c r="D76" s="21"/>
-      <c r="E76" s="47"/>
-      <c r="F76" s="48"/>
-      <c r="G76" s="10">
-        <f>IF(D76="P",1,0)</f>
-      </c>
-      <c r="H76" s="10">
-        <f>IF(D76="A",1,0)</f>
-      </c>
-      <c r="I76" s="10">
-        <f>IF(D76="L",1,0)</f>
+      <c r="E76" s="53"/>
+      <c r="F76" s="54"/>
+      <c r="G76" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H76" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I76" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J76" s="32"/>
       <c r="K76" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
-      <c r="A77" s="8">
-        <f>IF($B$8="","",$B$8+66)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B77" s="46">
-        <f>IF(A77="","",TEXT(A77,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A77" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B77" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C77" s="36"/>
       <c r="D77" s="21"/>
-      <c r="E77" s="47"/>
-      <c r="F77" s="48"/>
-      <c r="G77" s="10">
-        <f>IF(D77="P",1,0)</f>
-      </c>
-      <c r="H77" s="10">
-        <f>IF(D77="A",1,0)</f>
-      </c>
-      <c r="I77" s="10">
-        <f>IF(D77="L",1,0)</f>
+      <c r="E77" s="53"/>
+      <c r="F77" s="54"/>
+      <c r="G77" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H77" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I77" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J77" s="32"/>
       <c r="K77" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
-      <c r="A78" s="8">
-        <f>IF($B$8="","",$B$8+67)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B78" s="46">
-        <f>IF(A78="","",TEXT(A78,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A78" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B78" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C78" s="36"/>
       <c r="D78" s="21"/>
-      <c r="E78" s="47"/>
-      <c r="F78" s="48"/>
-      <c r="G78" s="10">
-        <f>IF(D78="P",1,0)</f>
-      </c>
-      <c r="H78" s="10">
-        <f>IF(D78="A",1,0)</f>
-      </c>
-      <c r="I78" s="10">
-        <f>IF(D78="L",1,0)</f>
+      <c r="E78" s="53"/>
+      <c r="F78" s="54"/>
+      <c r="G78" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H78" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I78" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J78" s="32"/>
       <c r="K78" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
-      <c r="A79" s="8">
-        <f>IF($B$8="","",$B$8+68)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B79" s="46">
-        <f>IF(A79="","",TEXT(A79,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A79" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B79" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C79" s="36"/>
       <c r="D79" s="21"/>
-      <c r="E79" s="47"/>
-      <c r="F79" s="48"/>
-      <c r="G79" s="10">
-        <f>IF(D79="P",1,0)</f>
-      </c>
-      <c r="H79" s="10">
-        <f>IF(D79="A",1,0)</f>
-      </c>
-      <c r="I79" s="10">
-        <f>IF(D79="L",1,0)</f>
+      <c r="E79" s="53"/>
+      <c r="F79" s="54"/>
+      <c r="G79" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H79" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I79" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J79" s="32"/>
       <c r="K79" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
-      <c r="A80" s="8">
-        <f>IF($B$8="","",$B$8+69)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B80" s="46">
-        <f>IF(A80="","",TEXT(A80,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A80" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B80" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C80" s="36"/>
       <c r="D80" s="21"/>
-      <c r="E80" s="47"/>
-      <c r="F80" s="48"/>
-      <c r="G80" s="10">
-        <f>IF(D80="P",1,0)</f>
-      </c>
-      <c r="H80" s="10">
-        <f>IF(D80="A",1,0)</f>
-      </c>
-      <c r="I80" s="10">
-        <f>IF(D80="L",1,0)</f>
+      <c r="E80" s="53"/>
+      <c r="F80" s="54"/>
+      <c r="G80" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H80" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I80" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J80" s="32"/>
       <c r="K80" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
-      <c r="A81" s="8">
-        <f>IF($B$8="","",$B$8+70)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B81" s="46">
-        <f>IF(A81="","",TEXT(A81,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A81" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B81" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C81" s="36"/>
       <c r="D81" s="21"/>
-      <c r="E81" s="47"/>
-      <c r="F81" s="48"/>
-      <c r="G81" s="10">
-        <f>IF(D81="P",1,0)</f>
-      </c>
-      <c r="H81" s="10">
-        <f>IF(D81="A",1,0)</f>
-      </c>
-      <c r="I81" s="10">
-        <f>IF(D81="L",1,0)</f>
+      <c r="E81" s="53"/>
+      <c r="F81" s="54"/>
+      <c r="G81" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H81" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I81" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J81" s="32"/>
       <c r="K81" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
-      <c r="A82" s="8">
-        <f>IF($B$8="","",$B$8+71)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B82" s="46">
-        <f>IF(A82="","",TEXT(A82,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A82" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B82" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C82" s="36"/>
       <c r="D82" s="21"/>
-      <c r="E82" s="47"/>
-      <c r="F82" s="48"/>
-      <c r="G82" s="10">
-        <f>IF(D82="P",1,0)</f>
-      </c>
-      <c r="H82" s="10">
-        <f>IF(D82="A",1,0)</f>
-      </c>
-      <c r="I82" s="10">
-        <f>IF(D82="L",1,0)</f>
+      <c r="E82" s="53"/>
+      <c r="F82" s="54"/>
+      <c r="G82" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H82" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I82" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J82" s="32"/>
       <c r="K82" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
-      <c r="A83" s="8">
-        <f>IF($B$8="","",$B$8+72)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B83" s="46">
-        <f>IF(A83="","",TEXT(A83,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A83" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B83" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C83" s="36"/>
       <c r="D83" s="21"/>
-      <c r="E83" s="47"/>
-      <c r="F83" s="48"/>
-      <c r="G83" s="10">
-        <f>IF(D83="P",1,0)</f>
-      </c>
-      <c r="H83" s="10">
-        <f>IF(D83="A",1,0)</f>
-      </c>
-      <c r="I83" s="10">
-        <f>IF(D83="L",1,0)</f>
+      <c r="E83" s="53"/>
+      <c r="F83" s="54"/>
+      <c r="G83" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H83" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I83" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J83" s="32"/>
       <c r="K83" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
-      <c r="A84" s="8">
-        <f>IF($B$8="","",$B$8+73)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B84" s="46">
-        <f>IF(A84="","",TEXT(A84,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A84" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B84" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C84" s="36"/>
       <c r="D84" s="21"/>
-      <c r="E84" s="47"/>
-      <c r="F84" s="48"/>
-      <c r="G84" s="10">
-        <f>IF(D84="P",1,0)</f>
-      </c>
-      <c r="H84" s="10">
-        <f>IF(D84="A",1,0)</f>
-      </c>
-      <c r="I84" s="10">
-        <f>IF(D84="L",1,0)</f>
+      <c r="E84" s="53"/>
+      <c r="F84" s="54"/>
+      <c r="G84" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H84" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I84" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J84" s="32"/>
       <c r="K84" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
-      <c r="A85" s="8">
-        <f>IF($B$8="","",$B$8+74)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B85" s="46">
-        <f>IF(A85="","",TEXT(A85,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A85" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B85" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C85" s="36"/>
       <c r="D85" s="21"/>
-      <c r="E85" s="47"/>
-      <c r="F85" s="48"/>
-      <c r="G85" s="10">
-        <f>IF(D85="P",1,0)</f>
-      </c>
-      <c r="H85" s="10">
-        <f>IF(D85="A",1,0)</f>
-      </c>
-      <c r="I85" s="10">
-        <f>IF(D85="L",1,0)</f>
+      <c r="E85" s="53"/>
+      <c r="F85" s="54"/>
+      <c r="G85" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H85" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I85" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J85" s="32"/>
       <c r="K85" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
-      <c r="A86" s="8">
-        <f>IF($B$8="","",$B$8+75)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B86" s="46">
-        <f>IF(A86="","",TEXT(A86,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A86" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B86" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C86" s="36"/>
       <c r="D86" s="21"/>
-      <c r="E86" s="47"/>
-      <c r="F86" s="48"/>
-      <c r="G86" s="10">
-        <f>IF(D86="P",1,0)</f>
-      </c>
-      <c r="H86" s="10">
-        <f>IF(D86="A",1,0)</f>
-      </c>
-      <c r="I86" s="10">
-        <f>IF(D86="L",1,0)</f>
+      <c r="E86" s="53"/>
+      <c r="F86" s="54"/>
+      <c r="G86" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H86" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I86" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J86" s="32"/>
       <c r="K86" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
-      <c r="A87" s="8">
-        <f>IF($B$8="","",$B$8+76)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B87" s="46">
-        <f>IF(A87="","",TEXT(A87,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A87" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B87" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C87" s="36"/>
       <c r="D87" s="21"/>
-      <c r="E87" s="47"/>
-      <c r="F87" s="48"/>
-      <c r="G87" s="10">
-        <f>IF(D87="P",1,0)</f>
-      </c>
-      <c r="H87" s="10">
-        <f>IF(D87="A",1,0)</f>
-      </c>
-      <c r="I87" s="10">
-        <f>IF(D87="L",1,0)</f>
+      <c r="E87" s="53"/>
+      <c r="F87" s="54"/>
+      <c r="G87" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H87" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I87" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J87" s="32"/>
       <c r="K87" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
-      <c r="A88" s="8">
-        <f>IF($B$8="","",$B$8+77)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B88" s="46">
-        <f>IF(A88="","",TEXT(A88,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A88" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B88" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C88" s="36"/>
       <c r="D88" s="21"/>
-      <c r="E88" s="47"/>
-      <c r="F88" s="48"/>
-      <c r="G88" s="10">
-        <f>IF(D88="P",1,0)</f>
-      </c>
-      <c r="H88" s="10">
-        <f>IF(D88="A",1,0)</f>
-      </c>
-      <c r="I88" s="10">
-        <f>IF(D88="L",1,0)</f>
+      <c r="E88" s="53"/>
+      <c r="F88" s="54"/>
+      <c r="G88" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H88" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I88" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J88" s="32"/>
       <c r="K88" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
-      <c r="A89" s="8">
-        <f>IF($B$8="","",$B$8+78)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B89" s="46">
-        <f>IF(A89="","",TEXT(A89,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A89" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B89" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C89" s="36"/>
       <c r="D89" s="21"/>
-      <c r="E89" s="47"/>
-      <c r="F89" s="48"/>
-      <c r="G89" s="10">
-        <f>IF(D89="P",1,0)</f>
-      </c>
-      <c r="H89" s="10">
-        <f>IF(D89="A",1,0)</f>
-      </c>
-      <c r="I89" s="10">
-        <f>IF(D89="L",1,0)</f>
+      <c r="E89" s="53"/>
+      <c r="F89" s="54"/>
+      <c r="G89" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H89" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I89" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J89" s="32"/>
       <c r="K89" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
-      <c r="A90" s="8">
-        <f>IF($B$8="","",$B$8+79)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B90" s="46">
-        <f>IF(A90="","",TEXT(A90,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A90" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B90" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C90" s="36"/>
       <c r="D90" s="21"/>
-      <c r="E90" s="47"/>
-      <c r="F90" s="48"/>
-      <c r="G90" s="10">
-        <f>IF(D90="P",1,0)</f>
-      </c>
-      <c r="H90" s="10">
-        <f>IF(D90="A",1,0)</f>
-      </c>
-      <c r="I90" s="10">
-        <f>IF(D90="L",1,0)</f>
+      <c r="E90" s="53"/>
+      <c r="F90" s="54"/>
+      <c r="G90" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H90" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I90" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J90" s="32"/>
       <c r="K90" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
-      <c r="A91" s="8">
-        <f>IF($B$8="","",$B$8+80)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B91" s="46">
-        <f>IF(A91="","",TEXT(A91,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A91" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B91" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C91" s="36"/>
       <c r="D91" s="21"/>
-      <c r="E91" s="47"/>
-      <c r="F91" s="48"/>
-      <c r="G91" s="10">
-        <f>IF(D91="P",1,0)</f>
-      </c>
-      <c r="H91" s="10">
-        <f>IF(D91="A",1,0)</f>
-      </c>
-      <c r="I91" s="10">
-        <f>IF(D91="L",1,0)</f>
+      <c r="E91" s="53"/>
+      <c r="F91" s="54"/>
+      <c r="G91" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H91" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I91" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J91" s="32"/>
       <c r="K91" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
-      <c r="A92" s="8">
-        <f>IF($B$8="","",$B$8+81)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B92" s="46">
-        <f>IF(A92="","",TEXT(A92,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A92" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B92" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C92" s="36"/>
       <c r="D92" s="21"/>
-      <c r="E92" s="47"/>
-      <c r="F92" s="48"/>
-      <c r="G92" s="10">
-        <f>IF(D92="P",1,0)</f>
-      </c>
-      <c r="H92" s="10">
-        <f>IF(D92="A",1,0)</f>
-      </c>
-      <c r="I92" s="10">
-        <f>IF(D92="L",1,0)</f>
+      <c r="E92" s="53"/>
+      <c r="F92" s="54"/>
+      <c r="G92" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H92" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I92" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J92" s="32"/>
       <c r="K92" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
-      <c r="A93" s="8">
-        <f>IF($B$8="","",$B$8+82)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B93" s="46">
-        <f>IF(A93="","",TEXT(A93,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A93" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B93" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C93" s="36"/>
       <c r="D93" s="21"/>
-      <c r="E93" s="47"/>
-      <c r="F93" s="48"/>
-      <c r="G93" s="10">
-        <f>IF(D93="P",1,0)</f>
-      </c>
-      <c r="H93" s="10">
-        <f>IF(D93="A",1,0)</f>
-      </c>
-      <c r="I93" s="10">
-        <f>IF(D93="L",1,0)</f>
+      <c r="E93" s="53"/>
+      <c r="F93" s="54"/>
+      <c r="G93" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H93" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I93" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J93" s="32"/>
       <c r="K93" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
-      <c r="A94" s="8">
-        <f>IF($B$8="","",$B$8+83)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B94" s="46">
-        <f>IF(A94="","",TEXT(A94,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A94" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B94" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C94" s="36"/>
       <c r="D94" s="21"/>
-      <c r="E94" s="47"/>
-      <c r="F94" s="48"/>
-      <c r="G94" s="10">
-        <f>IF(D94="P",1,0)</f>
-      </c>
-      <c r="H94" s="10">
-        <f>IF(D94="A",1,0)</f>
-      </c>
-      <c r="I94" s="10">
-        <f>IF(D94="L",1,0)</f>
+      <c r="E94" s="53"/>
+      <c r="F94" s="54"/>
+      <c r="G94" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H94" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I94" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J94" s="32"/>
       <c r="K94" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
-      <c r="A95" s="8">
-        <f>IF($B$8="","",$B$8+84)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B95" s="46">
-        <f>IF(A95="","",TEXT(A95,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A95" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B95" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C95" s="36"/>
       <c r="D95" s="21"/>
-      <c r="E95" s="47"/>
-      <c r="F95" s="48"/>
-      <c r="G95" s="10">
-        <f>IF(D95="P",1,0)</f>
-      </c>
-      <c r="H95" s="10">
-        <f>IF(D95="A",1,0)</f>
-      </c>
-      <c r="I95" s="10">
-        <f>IF(D95="L",1,0)</f>
+      <c r="E95" s="53"/>
+      <c r="F95" s="54"/>
+      <c r="G95" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H95" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I95" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J95" s="32"/>
       <c r="K95" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
-      <c r="A96" s="8">
-        <f>IF($B$8="","",$B$8+85)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B96" s="46">
-        <f>IF(A96="","",TEXT(A96,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A96" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B96" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C96" s="36"/>
       <c r="D96" s="21"/>
-      <c r="E96" s="47"/>
-      <c r="F96" s="48"/>
-      <c r="G96" s="10">
-        <f>IF(D96="P",1,0)</f>
-      </c>
-      <c r="H96" s="10">
-        <f>IF(D96="A",1,0)</f>
-      </c>
-      <c r="I96" s="10">
-        <f>IF(D96="L",1,0)</f>
+      <c r="E96" s="53"/>
+      <c r="F96" s="54"/>
+      <c r="G96" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H96" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I96" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J96" s="32"/>
       <c r="K96" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
-      <c r="A97" s="8">
-        <f>IF($B$8="","",$B$8+86)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B97" s="46">
-        <f>IF(A97="","",TEXT(A97,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A97" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B97" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C97" s="36"/>
       <c r="D97" s="21"/>
-      <c r="E97" s="47"/>
-      <c r="F97" s="48"/>
-      <c r="G97" s="10">
-        <f>IF(D97="P",1,0)</f>
-      </c>
-      <c r="H97" s="10">
-        <f>IF(D97="A",1,0)</f>
-      </c>
-      <c r="I97" s="10">
-        <f>IF(D97="L",1,0)</f>
+      <c r="E97" s="53"/>
+      <c r="F97" s="54"/>
+      <c r="G97" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H97" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I97" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J97" s="32"/>
       <c r="K97" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
-      <c r="A98" s="8">
-        <f>IF($B$8="","",$B$8+87)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B98" s="46">
-        <f>IF(A98="","",TEXT(A98,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A98" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B98" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C98" s="36"/>
       <c r="D98" s="21"/>
-      <c r="E98" s="47"/>
-      <c r="F98" s="48"/>
-      <c r="G98" s="10">
-        <f>IF(D98="P",1,0)</f>
-      </c>
-      <c r="H98" s="10">
-        <f>IF(D98="A",1,0)</f>
-      </c>
-      <c r="I98" s="10">
-        <f>IF(D98="L",1,0)</f>
+      <c r="E98" s="53"/>
+      <c r="F98" s="54"/>
+      <c r="G98" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H98" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I98" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J98" s="32"/>
       <c r="K98" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
-      <c r="A99" s="8">
-        <f>IF($B$8="","",$B$8+88)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B99" s="46">
-        <f>IF(A99="","",TEXT(A99,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A99" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B99" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C99" s="36"/>
       <c r="D99" s="21"/>
-      <c r="E99" s="47"/>
-      <c r="F99" s="48"/>
-      <c r="G99" s="10">
-        <f>IF(D99="P",1,0)</f>
-      </c>
-      <c r="H99" s="10">
-        <f>IF(D99="A",1,0)</f>
-      </c>
-      <c r="I99" s="10">
-        <f>IF(D99="L",1,0)</f>
+      <c r="E99" s="53"/>
+      <c r="F99" s="54"/>
+      <c r="G99" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H99" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I99" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J99" s="32"/>
       <c r="K99" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
-      <c r="A100" s="8">
-        <f>IF($B$8="","",$B$8+89)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B100" s="46">
-        <f>IF(A100="","",TEXT(A100,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A100" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B100" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C100" s="36"/>
       <c r="D100" s="21"/>
-      <c r="E100" s="47"/>
-      <c r="F100" s="48"/>
-      <c r="G100" s="10">
-        <f>IF(D100="P",1,0)</f>
-      </c>
-      <c r="H100" s="10">
-        <f>IF(D100="A",1,0)</f>
-      </c>
-      <c r="I100" s="10">
-        <f>IF(D100="L",1,0)</f>
+      <c r="E100" s="53"/>
+      <c r="F100" s="54"/>
+      <c r="G100" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H100" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I100" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J100" s="32"/>
       <c r="K100" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
-      <c r="A101" s="8">
-        <f>IF($B$8="","",$B$8+90)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B101" s="46">
-        <f>IF(A101="","",TEXT(A101,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A101" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B101" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C101" s="36"/>
       <c r="D101" s="21"/>
-      <c r="E101" s="47"/>
-      <c r="F101" s="48"/>
-      <c r="G101" s="10">
-        <f>IF(D101="P",1,0)</f>
-      </c>
-      <c r="H101" s="10">
-        <f>IF(D101="A",1,0)</f>
-      </c>
-      <c r="I101" s="10">
-        <f>IF(D101="L",1,0)</f>
+      <c r="E101" s="53"/>
+      <c r="F101" s="54"/>
+      <c r="G101" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H101" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I101" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J101" s="32"/>
       <c r="K101" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
-      <c r="A102" s="8">
-        <f>IF($B$8="","",$B$8+91)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B102" s="46">
-        <f>IF(A102="","",TEXT(A102,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A102" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B102" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C102" s="36"/>
       <c r="D102" s="21"/>
-      <c r="E102" s="47"/>
-      <c r="F102" s="48"/>
-      <c r="G102" s="10">
-        <f>IF(D102="P",1,0)</f>
-      </c>
-      <c r="H102" s="10">
-        <f>IF(D102="A",1,0)</f>
-      </c>
-      <c r="I102" s="10">
-        <f>IF(D102="L",1,0)</f>
+      <c r="E102" s="53"/>
+      <c r="F102" s="54"/>
+      <c r="G102" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H102" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I102" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J102" s="32"/>
       <c r="K102" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
-      <c r="A103" s="8">
-        <f>IF($B$8="","",$B$8+92)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B103" s="46">
-        <f>IF(A103="","",TEXT(A103,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A103" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B103" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C103" s="36"/>
       <c r="D103" s="21"/>
-      <c r="E103" s="47"/>
-      <c r="F103" s="48"/>
-      <c r="G103" s="10">
-        <f>IF(D103="P",1,0)</f>
-      </c>
-      <c r="H103" s="10">
-        <f>IF(D103="A",1,0)</f>
-      </c>
-      <c r="I103" s="10">
-        <f>IF(D103="L",1,0)</f>
+      <c r="E103" s="53"/>
+      <c r="F103" s="54"/>
+      <c r="G103" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H103" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I103" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J103" s="32"/>
       <c r="K103" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
-      <c r="A104" s="8">
-        <f>IF($B$8="","",$B$8+93)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B104" s="46">
-        <f>IF(A104="","",TEXT(A104,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A104" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B104" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C104" s="36"/>
       <c r="D104" s="21"/>
-      <c r="E104" s="47"/>
-      <c r="F104" s="48"/>
-      <c r="G104" s="10">
-        <f>IF(D104="P",1,0)</f>
-      </c>
-      <c r="H104" s="10">
-        <f>IF(D104="A",1,0)</f>
-      </c>
-      <c r="I104" s="10">
-        <f>IF(D104="L",1,0)</f>
+      <c r="E104" s="53"/>
+      <c r="F104" s="54"/>
+      <c r="G104" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H104" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I104" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J104" s="32"/>
       <c r="K104" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
-      <c r="A105" s="8">
-        <f>IF($B$8="","",$B$8+94)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B105" s="46">
-        <f>IF(A105="","",TEXT(A105,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A105" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B105" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C105" s="36"/>
       <c r="D105" s="21"/>
-      <c r="E105" s="47"/>
-      <c r="F105" s="48"/>
-      <c r="G105" s="10">
-        <f>IF(D105="P",1,0)</f>
-      </c>
-      <c r="H105" s="10">
-        <f>IF(D105="A",1,0)</f>
-      </c>
-      <c r="I105" s="10">
-        <f>IF(D105="L",1,0)</f>
+      <c r="E105" s="53"/>
+      <c r="F105" s="54"/>
+      <c r="G105" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H105" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I105" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J105" s="32"/>
       <c r="K105" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
-      <c r="A106" s="8">
-        <f>IF($B$8="","",$B$8+95)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B106" s="46">
-        <f>IF(A106="","",TEXT(A106,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A106" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B106" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C106" s="36"/>
       <c r="D106" s="21"/>
-      <c r="E106" s="47"/>
-      <c r="F106" s="48"/>
-      <c r="G106" s="10">
-        <f>IF(D106="P",1,0)</f>
-      </c>
-      <c r="H106" s="10">
-        <f>IF(D106="A",1,0)</f>
-      </c>
-      <c r="I106" s="10">
-        <f>IF(D106="L",1,0)</f>
+      <c r="E106" s="53"/>
+      <c r="F106" s="54"/>
+      <c r="G106" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H106" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I106" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J106" s="32"/>
       <c r="K106" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
-      <c r="A107" s="8">
-        <f>IF($B$8="","",$B$8+96)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B107" s="46">
-        <f>IF(A107="","",TEXT(A107,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A107" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B107" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C107" s="36"/>
       <c r="D107" s="21"/>
-      <c r="E107" s="47"/>
-      <c r="F107" s="48"/>
-      <c r="G107" s="10">
-        <f>IF(D107="P",1,0)</f>
-      </c>
-      <c r="H107" s="10">
-        <f>IF(D107="A",1,0)</f>
-      </c>
-      <c r="I107" s="10">
-        <f>IF(D107="L",1,0)</f>
+      <c r="E107" s="53"/>
+      <c r="F107" s="54"/>
+      <c r="G107" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H107" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I107" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J107" s="32"/>
       <c r="K107" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
-      <c r="A108" s="8">
-        <f>IF($B$8="","",$B$8+97)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B108" s="46">
-        <f>IF(A108="","",TEXT(A108,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A108" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B108" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C108" s="36"/>
       <c r="D108" s="21"/>
-      <c r="E108" s="47"/>
-      <c r="F108" s="48"/>
-      <c r="G108" s="10">
-        <f>IF(D108="P",1,0)</f>
-      </c>
-      <c r="H108" s="10">
-        <f>IF(D108="A",1,0)</f>
-      </c>
-      <c r="I108" s="10">
-        <f>IF(D108="L",1,0)</f>
+      <c r="E108" s="53"/>
+      <c r="F108" s="54"/>
+      <c r="G108" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H108" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I108" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J108" s="32"/>
       <c r="K108" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
-      <c r="A109" s="8">
-        <f>IF($B$8="","",$B$8+98)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B109" s="46">
-        <f>IF(A109="","",TEXT(A109,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A109" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B109" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C109" s="36"/>
       <c r="D109" s="21"/>
-      <c r="E109" s="47"/>
-      <c r="F109" s="48"/>
-      <c r="G109" s="10">
-        <f>IF(D109="P",1,0)</f>
-      </c>
-      <c r="H109" s="10">
-        <f>IF(D109="A",1,0)</f>
-      </c>
-      <c r="I109" s="10">
-        <f>IF(D109="L",1,0)</f>
+      <c r="E109" s="53"/>
+      <c r="F109" s="54"/>
+      <c r="G109" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H109" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I109" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J109" s="32"/>
       <c r="K109" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
-      <c r="A110" s="8">
-        <f>IF($B$8="","",$B$8+99)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B110" s="46">
-        <f>IF(A110="","",TEXT(A110,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A110" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B110" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C110" s="36"/>
       <c r="D110" s="21"/>
-      <c r="E110" s="47"/>
-      <c r="F110" s="48"/>
-      <c r="G110" s="10">
-        <f>IF(D110="P",1,0)</f>
-      </c>
-      <c r="H110" s="10">
-        <f>IF(D110="A",1,0)</f>
-      </c>
-      <c r="I110" s="10">
-        <f>IF(D110="L",1,0)</f>
+      <c r="E110" s="53"/>
+      <c r="F110" s="54"/>
+      <c r="G110" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H110" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I110" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J110" s="32"/>
       <c r="K110" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
-      <c r="A111" s="8">
-        <f>IF($B$8="","",$B$8+100)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B111" s="46">
-        <f>IF(A111="","",TEXT(A111,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A111" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B111" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C111" s="36"/>
       <c r="D111" s="21"/>
-      <c r="E111" s="47"/>
-      <c r="F111" s="48"/>
-      <c r="G111" s="10">
-        <f>IF(D111="P",1,0)</f>
-      </c>
-      <c r="H111" s="10">
-        <f>IF(D111="A",1,0)</f>
-      </c>
-      <c r="I111" s="10">
-        <f>IF(D111="L",1,0)</f>
+      <c r="E111" s="53"/>
+      <c r="F111" s="54"/>
+      <c r="G111" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H111" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I111" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J111" s="32"/>
       <c r="K111" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
-      <c r="A112" s="8">
-        <f>IF($B$8="","",$B$8+101)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B112" s="46">
-        <f>IF(A112="","",TEXT(A112,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A112" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B112" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C112" s="36"/>
       <c r="D112" s="21"/>
-      <c r="E112" s="47"/>
-      <c r="F112" s="48"/>
-      <c r="G112" s="10">
-        <f>IF(D112="P",1,0)</f>
-      </c>
-      <c r="H112" s="10">
-        <f>IF(D112="A",1,0)</f>
-      </c>
-      <c r="I112" s="10">
-        <f>IF(D112="L",1,0)</f>
+      <c r="E112" s="53"/>
+      <c r="F112" s="54"/>
+      <c r="G112" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H112" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I112" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J112" s="32"/>
       <c r="K112" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
-      <c r="A113" s="8">
-        <f>IF($B$8="","",$B$8+102)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B113" s="46">
-        <f>IF(A113="","",TEXT(A113,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A113" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B113" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C113" s="36"/>
       <c r="D113" s="21"/>
-      <c r="E113" s="47"/>
-      <c r="F113" s="48"/>
-      <c r="G113" s="10">
-        <f>IF(D113="P",1,0)</f>
-      </c>
-      <c r="H113" s="10">
-        <f>IF(D113="A",1,0)</f>
-      </c>
-      <c r="I113" s="10">
-        <f>IF(D113="L",1,0)</f>
+      <c r="E113" s="53"/>
+      <c r="F113" s="54"/>
+      <c r="G113" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H113" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I113" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J113" s="32"/>
       <c r="K113" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
-      <c r="A114" s="8">
-        <f>IF($B$8="","",$B$8+103)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B114" s="46">
-        <f>IF(A114="","",TEXT(A114,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A114" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B114" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C114" s="36"/>
       <c r="D114" s="21"/>
-      <c r="E114" s="47"/>
-      <c r="F114" s="48"/>
-      <c r="G114" s="10">
-        <f>IF(D114="P",1,0)</f>
-      </c>
-      <c r="H114" s="10">
-        <f>IF(D114="A",1,0)</f>
-      </c>
-      <c r="I114" s="10">
-        <f>IF(D114="L",1,0)</f>
+      <c r="E114" s="53"/>
+      <c r="F114" s="54"/>
+      <c r="G114" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H114" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I114" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J114" s="32"/>
       <c r="K114" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
-      <c r="A115" s="8">
-        <f>IF($B$8="","",$B$8+104)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B115" s="46">
-        <f>IF(A115="","",TEXT(A115,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A115" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B115" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C115" s="36"/>
       <c r="D115" s="21"/>
-      <c r="E115" s="47"/>
-      <c r="F115" s="48"/>
-      <c r="G115" s="10">
-        <f>IF(D115="P",1,0)</f>
-      </c>
-      <c r="H115" s="10">
-        <f>IF(D115="A",1,0)</f>
-      </c>
-      <c r="I115" s="10">
-        <f>IF(D115="L",1,0)</f>
+      <c r="E115" s="53"/>
+      <c r="F115" s="54"/>
+      <c r="G115" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H115" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I115" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J115" s="32"/>
       <c r="K115" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
-      <c r="A116" s="8">
-        <f>IF($B$8="","",$B$8+105)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B116" s="46">
-        <f>IF(A116="","",TEXT(A116,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A116" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B116" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C116" s="36"/>
       <c r="D116" s="21"/>
-      <c r="E116" s="47"/>
-      <c r="F116" s="48"/>
-      <c r="G116" s="10">
-        <f>IF(D116="P",1,0)</f>
-      </c>
-      <c r="H116" s="10">
-        <f>IF(D116="A",1,0)</f>
-      </c>
-      <c r="I116" s="10">
-        <f>IF(D116="L",1,0)</f>
+      <c r="E116" s="53"/>
+      <c r="F116" s="54"/>
+      <c r="G116" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H116" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I116" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J116" s="32"/>
       <c r="K116" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
-      <c r="A117" s="8">
-        <f>IF($B$8="","",$B$8+106)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B117" s="46">
-        <f>IF(A117="","",TEXT(A117,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A117" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B117" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C117" s="36"/>
       <c r="D117" s="21"/>
-      <c r="E117" s="47"/>
-      <c r="F117" s="48"/>
-      <c r="G117" s="10">
-        <f>IF(D117="P",1,0)</f>
-      </c>
-      <c r="H117" s="10">
-        <f>IF(D117="A",1,0)</f>
-      </c>
-      <c r="I117" s="10">
-        <f>IF(D117="L",1,0)</f>
+      <c r="E117" s="53"/>
+      <c r="F117" s="54"/>
+      <c r="G117" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H117" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I117" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J117" s="32"/>
       <c r="K117" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75">
-      <c r="A118" s="8">
-        <f>IF($B$8="","",$B$8+107)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B118" s="46">
-        <f>IF(A118="","",TEXT(A118,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A118" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B118" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C118" s="36"/>
       <c r="D118" s="21"/>
-      <c r="E118" s="47"/>
-      <c r="F118" s="48"/>
-      <c r="G118" s="10">
-        <f>IF(D118="P",1,0)</f>
-      </c>
-      <c r="H118" s="10">
-        <f>IF(D118="A",1,0)</f>
-      </c>
-      <c r="I118" s="10">
-        <f>IF(D118="L",1,0)</f>
+      <c r="E118" s="53"/>
+      <c r="F118" s="54"/>
+      <c r="G118" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H118" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I118" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J118" s="32"/>
       <c r="K118" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
-      <c r="A119" s="8">
-        <f>IF($B$8="","",$B$8+108)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B119" s="46">
-        <f>IF(A119="","",TEXT(A119,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A119" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B119" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C119" s="36"/>
       <c r="D119" s="21"/>
-      <c r="E119" s="47"/>
-      <c r="F119" s="48"/>
-      <c r="G119" s="10">
-        <f>IF(D119="P",1,0)</f>
-      </c>
-      <c r="H119" s="10">
-        <f>IF(D119="A",1,0)</f>
-      </c>
-      <c r="I119" s="10">
-        <f>IF(D119="L",1,0)</f>
+      <c r="E119" s="53"/>
+      <c r="F119" s="54"/>
+      <c r="G119" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H119" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I119" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J119" s="32"/>
       <c r="K119" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
-      <c r="A120" s="8">
-        <f>IF($B$8="","",$B$8+109)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B120" s="46">
-        <f>IF(A120="","",TEXT(A120,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A120" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B120" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C120" s="36"/>
       <c r="D120" s="21"/>
-      <c r="E120" s="47"/>
-      <c r="F120" s="48"/>
-      <c r="G120" s="10">
-        <f>IF(D120="P",1,0)</f>
-      </c>
-      <c r="H120" s="10">
-        <f>IF(D120="A",1,0)</f>
-      </c>
-      <c r="I120" s="10">
-        <f>IF(D120="L",1,0)</f>
+      <c r="E120" s="53"/>
+      <c r="F120" s="54"/>
+      <c r="G120" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H120" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I120" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J120" s="32"/>
       <c r="K120" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75">
-      <c r="A121" s="8">
-        <f>IF($B$8="","",$B$8+110)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B121" s="46">
-        <f>IF(A121="","",TEXT(A121,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A121" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B121" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C121" s="36"/>
       <c r="D121" s="21"/>
-      <c r="E121" s="47"/>
-      <c r="F121" s="48"/>
-      <c r="G121" s="10">
-        <f>IF(D121="P",1,0)</f>
-      </c>
-      <c r="H121" s="10">
-        <f>IF(D121="A",1,0)</f>
-      </c>
-      <c r="I121" s="10">
-        <f>IF(D121="L",1,0)</f>
+      <c r="E121" s="53"/>
+      <c r="F121" s="54"/>
+      <c r="G121" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H121" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I121" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J121" s="32"/>
       <c r="K121" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="18.75">
-      <c r="A122" s="8">
-        <f>IF($B$8="","",$B$8+111)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B122" s="46">
-        <f>IF(A122="","",TEXT(A122,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A122" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B122" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C122" s="36"/>
       <c r="D122" s="21"/>
-      <c r="E122" s="47"/>
-      <c r="F122" s="48"/>
-      <c r="G122" s="10">
-        <f>IF(D122="P",1,0)</f>
-      </c>
-      <c r="H122" s="10">
-        <f>IF(D122="A",1,0)</f>
-      </c>
-      <c r="I122" s="10">
-        <f>IF(D122="L",1,0)</f>
+      <c r="E122" s="53"/>
+      <c r="F122" s="54"/>
+      <c r="G122" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H122" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I122" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J122" s="32"/>
       <c r="K122" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18.75">
-      <c r="A123" s="8">
-        <f>IF($B$8="","",$B$8+112)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B123" s="46">
-        <f>IF(A123="","",TEXT(A123,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A123" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B123" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C123" s="36"/>
       <c r="D123" s="21"/>
-      <c r="E123" s="47"/>
-      <c r="F123" s="48"/>
-      <c r="G123" s="10">
-        <f>IF(D123="P",1,0)</f>
-      </c>
-      <c r="H123" s="10">
-        <f>IF(D123="A",1,0)</f>
-      </c>
-      <c r="I123" s="10">
-        <f>IF(D123="L",1,0)</f>
+      <c r="E123" s="53"/>
+      <c r="F123" s="54"/>
+      <c r="G123" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H123" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I123" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J123" s="32"/>
       <c r="K123" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18.75">
-      <c r="A124" s="8">
-        <f>IF($B$8="","",$B$8+113)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B124" s="46">
-        <f>IF(A124="","",TEXT(A124,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A124" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B124" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C124" s="36"/>
       <c r="D124" s="21"/>
-      <c r="E124" s="47"/>
-      <c r="F124" s="48"/>
-      <c r="G124" s="10">
-        <f>IF(D124="P",1,0)</f>
-      </c>
-      <c r="H124" s="10">
-        <f>IF(D124="A",1,0)</f>
-      </c>
-      <c r="I124" s="10">
-        <f>IF(D124="L",1,0)</f>
+      <c r="E124" s="53"/>
+      <c r="F124" s="54"/>
+      <c r="G124" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H124" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I124" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J124" s="32"/>
       <c r="K124" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="18.75">
-      <c r="A125" s="8">
-        <f>IF($B$8="","",$B$8+114)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B125" s="46">
-        <f>IF(A125="","",TEXT(A125,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A125" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B125" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C125" s="36"/>
       <c r="D125" s="21"/>
-      <c r="E125" s="47"/>
-      <c r="F125" s="48"/>
-      <c r="G125" s="10">
-        <f>IF(D125="P",1,0)</f>
-      </c>
-      <c r="H125" s="10">
-        <f>IF(D125="A",1,0)</f>
-      </c>
-      <c r="I125" s="10">
-        <f>IF(D125="L",1,0)</f>
+      <c r="E125" s="53"/>
+      <c r="F125" s="54"/>
+      <c r="G125" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H125" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I125" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J125" s="32"/>
       <c r="K125" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="18.75">
-      <c r="A126" s="8">
-        <f>IF($B$8="","",$B$8+115)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B126" s="46">
-        <f>IF(A126="","",TEXT(A126,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A126" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B126" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C126" s="36"/>
       <c r="D126" s="21"/>
-      <c r="E126" s="47"/>
-      <c r="F126" s="48"/>
-      <c r="G126" s="10">
-        <f>IF(D126="P",1,0)</f>
-      </c>
-      <c r="H126" s="10">
-        <f>IF(D126="A",1,0)</f>
-      </c>
-      <c r="I126" s="10">
-        <f>IF(D126="L",1,0)</f>
+      <c r="E126" s="53"/>
+      <c r="F126" s="54"/>
+      <c r="G126" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H126" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I126" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J126" s="32"/>
       <c r="K126" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18.75">
-      <c r="A127" s="8">
-        <f>IF($B$8="","",$B$8+116)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B127" s="46">
-        <f>IF(A127="","",TEXT(A127,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A127" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B127" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C127" s="36"/>
       <c r="D127" s="21"/>
-      <c r="E127" s="47"/>
-      <c r="F127" s="48"/>
-      <c r="G127" s="10">
-        <f>IF(D127="P",1,0)</f>
-      </c>
-      <c r="H127" s="10">
-        <f>IF(D127="A",1,0)</f>
-      </c>
-      <c r="I127" s="10">
-        <f>IF(D127="L",1,0)</f>
+      <c r="E127" s="53"/>
+      <c r="F127" s="54"/>
+      <c r="G127" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H127" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I127" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J127" s="32"/>
       <c r="K127" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="18.75">
-      <c r="A128" s="8">
-        <f>IF($B$8="","",$B$8+117)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B128" s="46">
-        <f>IF(A128="","",TEXT(A128,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A128" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B128" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C128" s="36"/>
       <c r="D128" s="21"/>
-      <c r="E128" s="47"/>
-      <c r="F128" s="48"/>
-      <c r="G128" s="10">
-        <f>IF(D128="P",1,0)</f>
-      </c>
-      <c r="H128" s="10">
-        <f>IF(D128="A",1,0)</f>
-      </c>
-      <c r="I128" s="10">
-        <f>IF(D128="L",1,0)</f>
+      <c r="E128" s="53"/>
+      <c r="F128" s="54"/>
+      <c r="G128" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H128" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I128" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J128" s="32"/>
       <c r="K128" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18.75">
-      <c r="A129" s="8">
-        <f>IF($B$8="","",$B$8+118)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B129" s="46">
-        <f>IF(A129="","",TEXT(A129,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A129" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B129" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C129" s="36"/>
       <c r="D129" s="21"/>
-      <c r="E129" s="47"/>
-      <c r="F129" s="48"/>
-      <c r="G129" s="10">
-        <f>IF(D129="P",1,0)</f>
-      </c>
-      <c r="H129" s="10">
-        <f>IF(D129="A",1,0)</f>
-      </c>
-      <c r="I129" s="10">
-        <f>IF(D129="L",1,0)</f>
+      <c r="E129" s="53"/>
+      <c r="F129" s="54"/>
+      <c r="G129" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H129" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I129" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J129" s="32"/>
       <c r="K129" s="32"/>
     </row>
     <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="18.75">
-      <c r="A130" s="8">
-        <f>IF($B$8="","",$B$8+119)</f>
-        <v>25569.229166666668</v>
-      </c>
-      <c r="B130" s="46">
-        <f>IF(A130="","",TEXT(A130,"ddd"))</f>
-        <v>25569.229166666668</v>
+      <c r="A130" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B130" s="50" t="s">
+        <v>24</v>
       </c>
       <c r="C130" s="36"/>
       <c r="D130" s="21"/>
-      <c r="E130" s="47"/>
-      <c r="F130" s="48"/>
-      <c r="G130" s="10">
-        <f>IF(D130="P",1,0)</f>
-      </c>
-      <c r="H130" s="10">
-        <f>IF(D130="A",1,0)</f>
-      </c>
-      <c r="I130" s="10">
-        <f>IF(D130="L",1,0)</f>
+      <c r="E130" s="53"/>
+      <c r="F130" s="54"/>
+      <c r="G130" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="H130" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="I130" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="J130" s="32"/>
       <c r="K130" s="32"/>
@@ -4195,18 +3845,18 @@
       <c r="J132" s="32"/>
       <c r="K132" s="32"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75" customFormat="1" s="40">
-      <c r="A133" s="51" t="s">
-        <v>57</v>
-      </c>
-      <c r="B133" s="52"/>
+    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75" customFormat="1" s="43">
+      <c r="A133" s="58" t="s">
+        <v>24</v>
+      </c>
+      <c r="B133" s="59"/>
       <c r="C133" s="32"/>
       <c r="D133" s="32"/>
-      <c r="E133" s="53"/>
-      <c r="F133" s="53"/>
-      <c r="G133" s="54"/>
-      <c r="H133" s="54"/>
-      <c r="I133" s="54"/>
+      <c r="E133" s="60"/>
+      <c r="F133" s="60"/>
+      <c r="G133" s="61"/>
+      <c r="H133" s="61"/>
+      <c r="I133" s="61"/>
       <c r="J133" s="32"/>
       <c r="K133" s="32"/>
     </row>
